--- a/LINT/outputs/lint_review.xlsx
+++ b/LINT/outputs/lint_review.xlsx
@@ -262,47 +262,165 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
+    <comment ref="M2" authorId="0">
+      <text>
+        <t xml:space="preserve">Primary waiver rule shared by 32 issues.
+Shared issue IDs: DeadCode-ML_e84cae0edf25, DeadCode-ML_7fbcfb987ea2, DeadCode-ML_4061be3b213d, DeadCode-ML_37ccad7cafff, DeadCode-ML_5355615cf12e, DeadCode-ML_f4b3854a503a, DeadCode-ML_515337bfea90, DeadCode-ML_097ffa5f22ec, DeadCode-ML_51ab66d6b498, DeadCode-ML_14a921a01cb4, DeadCode-ML_6817476ffd8b, DeadCode-ML_1763cba8fabb, DeadCode-ML_4eb385741c5b, DeadCode-ML_fcc27bcb35f3, DeadCode-ML_9f84acebc779, DeadCode-ML_320417ba96fc, DeadCode-ML_8a1be6df56cf, DeadCode-ML_3f40c134f801, DeadCode-ML_520b0d4a7048, DeadCode-ML_fbb63c7ca9b7, DeadCode-ML_164f1d6db727, DeadCode-ML_323fbdc90de8, DeadCode-ML_75c765148170, DeadCode-ML_989754a375df, DeadCode-ML_c811eb95211b, DeadCode-ML_a870b15ab72f, DeadCode-ML_e22b6a54e417, DeadCode-ML_28eef1dad7ca, DeadCode-ML_366797be4f73, DeadCode-ML_c2740f9a65ca, DeadCode-ML_d48f18b9af6a</t>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
     <comment ref="M4" authorId="0">
       <text>
-        <t xml:space="preserve">Primary waiver rule shared by 4 issues.
-Shared issue IDs: DeadCode-ML_4061be3b213d, DeadCode-ML_37ccad7cafff, DeadCode-ML_5355615cf12e</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
       </text>
     </comment>
     <comment ref="M5" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_741 with primary issue DeadCode-ML_7fbcfb987ea2.</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
       </text>
     </comment>
     <comment ref="M6" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_741 with primary issue DeadCode-ML_7fbcfb987ea2.</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
       </text>
     </comment>
     <comment ref="M7" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_741 with primary issue DeadCode-ML_7fbcfb987ea2.</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M8" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M9" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M10" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
       </text>
     </comment>
     <comment ref="M11" authorId="0">
       <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: DeadCode-ML_14a921a01cb4</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
       </text>
     </comment>
     <comment ref="M12" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_748 with primary issue DeadCode-ML_51ab66d6b498.</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M13" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M14" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M15" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M16" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M17" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M18" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M19" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M20" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M21" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M22" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M23" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M24" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M25" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M26" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M27" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M28" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M29" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
       </text>
     </comment>
     <comment ref="M30" authorId="0">
       <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: DeadCode-ML_366797be4f73</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
       </text>
     </comment>
     <comment ref="M31" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_767 with primary issue DeadCode-ML_28eef1dad7ca.</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M32" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+      </text>
+    </comment>
+    <comment ref="M33" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
       </text>
     </comment>
   </commentList>
@@ -548,48 +666,285 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
+    <comment ref="M2" authorId="0">
+      <text>
+        <t xml:space="preserve">Primary waiver rule shared by 56 issues.
+Shared issue IDs: W164a_fd6a370a79ab, W164a_d93541370b31, W164a_7660b53e6188, W164a_c90a63b2d9e8, W164a_1d457f0d51fe, W164a_c078e63cfa3e, W164a_b1c30aa3f537, W164a_b16c35b5e10c, W164a_017526ab4c3d, W164a_c505e9870872, W164a_14c860086292, W164a_411e166bb6e8, W164a_97e34627177b, W164a_b105ea5a36d7, W164a_af9f5f624f8c, W164a_1064ea20e23f, W164a_f303846eddbf, W164a_1ab2b57028bc, W164a_d33034023f51, W164a_8efcf1475d55, W164a_043a813ca8f6, W164a_72d36f1914f2, W164a_e97c355c8578, W164a_8ae0b89979a0, W164a_4f28e5ce8f80, W164a_2cf4a06f09c5, W164a_5e0b6dc4ac33, W164a_4e84e698ed3e, W164a_a0c63c9da2e6, W164a_6fc4541b3f0d, W164a_453183e95577, W164a_4a2e5e0663a5, W164a_6ff437a3ada4, W164a_161793cb7dad, W164a_ebd65b48e89f, W164a_dc52da86c0c0, W164a_6fda0611280a, W164a_ea91e32f9aa7, W164a_ccf02468d9ed, W164a_6baf6e5ad83d, W164a_ad7c6281ae5d, W164a_4f36dd084a7e, W164a_fcad9e726414, W164a_f08d25377633, W164a_fe2225ff642e, W164a_33135cff7657, W164a_d681159d5355, W164a_d4ea1a544292, W164a_911d84fd734b, W164a_c236385e4a5a, W164a_87f654826bb3, W164a_f0e03f5a7b78, W164a_25c7ecc3014c, W164a_f4629a2c0a13, W164a_40e2f3cc3783</t>
+      </text>
+    </comment>
+    <comment ref="M3" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M4" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M5" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M6" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
     <comment ref="M7" authorId="0">
       <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: W164a_c078e63cfa3e</t>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
       </text>
     </comment>
     <comment ref="M8" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule W164a_811 with primary issue W164a_1d457f0d51fe.</t>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M9" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M10" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M11" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M12" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
       </text>
     </comment>
     <comment ref="M13" authorId="0">
       <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: W164a_411e166bb6e8</t>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
       </text>
     </comment>
     <comment ref="M14" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule W164a_791 with primary issue W164a_14c860086292.</t>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
       </text>
     </comment>
     <comment ref="M15" authorId="0">
       <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: W164a_b105ea5a36d7</t>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
       </text>
     </comment>
     <comment ref="M16" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule W164a_793 with primary issue W164a_97e34627177b.</t>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M17" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M18" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
       </text>
     </comment>
     <comment ref="M19" authorId="0">
       <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: W164a_1ab2b57028bc</t>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
       </text>
     </comment>
     <comment ref="M20" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule W164a_785 with primary issue W164a_f303846eddbf.</t>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M21" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M22" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M23" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M24" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M25" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M26" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M27" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M28" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M29" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M30" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M31" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M32" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M33" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M34" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M35" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M36" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M37" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M38" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M39" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M40" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M41" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M42" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M43" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M44" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M45" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M46" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M47" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M48" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M49" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M50" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M51" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M52" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M53" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M54" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M55" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M56" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+      </text>
+    </comment>
+    <comment ref="M57" authorId="0">
+      <text>
+        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
       </text>
     </comment>
   </commentList>
@@ -18452,7 +18807,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module, LineNumber, Statement, NodeType, PropertyList:LintPropertyName=Property_142</t>
+          <t xml:space="preserve">Goal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -18502,7 +18857,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-2026 13:10:10</t>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -18814,12 +19169,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -18864,12 +19219,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -18946,12 +19301,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -18986,7 +19341,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_740</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -18996,12 +19351,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -19078,12 +19433,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19118,7 +19473,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_741</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -19128,12 +19483,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -19210,12 +19565,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19250,7 +19605,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_741</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -19260,12 +19615,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -19342,12 +19697,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19382,7 +19737,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_741</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -19392,12 +19747,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -19474,12 +19829,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19514,7 +19869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_741</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -19524,12 +19879,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -19606,12 +19961,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19646,7 +20001,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_745</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -19656,12 +20011,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -19738,12 +20093,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19778,7 +20133,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_746</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -19788,12 +20143,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -19870,12 +20225,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -19910,7 +20265,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_747</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -19920,12 +20275,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -20002,12 +20357,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20042,7 +20397,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_748</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -20052,12 +20407,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -20134,12 +20489,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20174,7 +20529,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_748</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -20184,12 +20539,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -20266,12 +20621,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -20306,7 +20661,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_750</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -20316,12 +20671,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -20398,12 +20753,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -20438,7 +20793,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_763</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -20448,12 +20803,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -20530,12 +20885,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -20570,7 +20925,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_764</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -20580,12 +20935,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -20662,12 +21017,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -20702,7 +21057,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_765</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -20712,12 +21067,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -20794,12 +21149,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -20834,7 +21189,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_766</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -20844,12 +21199,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -20926,12 +21281,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -20966,7 +21321,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_751</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -20976,12 +21331,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -21058,12 +21413,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -21098,7 +21453,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_752</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -21108,12 +21463,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -21190,12 +21545,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -21230,7 +21585,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_753</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -21240,12 +21595,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -21322,12 +21677,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -21362,7 +21717,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_754</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -21372,12 +21727,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -21454,12 +21809,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -21494,7 +21849,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_755</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -21504,12 +21859,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -21586,12 +21941,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -21626,7 +21981,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_756</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -21636,12 +21991,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -21718,12 +22073,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -21758,7 +22113,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_757</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -21768,12 +22123,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -21850,12 +22205,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -21890,7 +22245,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_758</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -21900,12 +22255,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -21982,12 +22337,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -22022,7 +22377,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_759</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -22032,12 +22387,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -22114,12 +22469,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -22154,7 +22509,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_760</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -22164,12 +22519,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -22246,12 +22601,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -22286,7 +22641,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_761</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -22296,12 +22651,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -22378,12 +22733,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -22418,7 +22773,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_762</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -22428,12 +22783,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -22510,12 +22865,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -22550,7 +22905,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_767</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -22560,12 +22915,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -22642,12 +22997,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -22682,7 +23037,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_767</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -22692,12 +23047,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -22774,12 +23129,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -22814,7 +23169,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_769</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -22824,12 +23179,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -22906,12 +23261,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -22946,7 +23301,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_770</t>
+          <t xml:space="preserve">DeadCode-ML_739</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -22956,12 +23311,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -25745,12 +26100,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -25795,12 +26150,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -25902,12 +26257,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -25942,7 +26297,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_809</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -25952,12 +26307,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -26059,12 +26414,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -26099,7 +26454,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_814</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -26109,12 +26464,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -26216,12 +26571,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -26256,7 +26611,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_810</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -26266,12 +26621,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -26373,12 +26728,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -26413,7 +26768,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_813</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -26423,12 +26778,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -26530,12 +26885,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -26570,7 +26925,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_811</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -26580,12 +26935,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -26687,12 +27042,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -26727,7 +27082,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_811</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -26737,12 +27092,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -26844,12 +27199,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -26884,7 +27239,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_781</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -26894,12 +27249,12 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -27001,12 +27356,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -27041,7 +27396,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_815</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -27051,12 +27406,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -27158,12 +27513,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -27198,7 +27553,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_789</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -27208,12 +27563,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -27315,12 +27670,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -27355,7 +27710,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_790</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -27365,12 +27720,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -27472,12 +27827,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -27512,7 +27867,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_791</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -27522,12 +27877,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -27629,12 +27984,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -27669,7 +28024,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_791</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -27679,12 +28034,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -27786,12 +28141,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -27826,7 +28181,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_793</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -27836,12 +28191,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -27943,12 +28298,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -27983,7 +28338,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_793</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -27993,12 +28348,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -28100,12 +28455,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -28140,7 +28495,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_783</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -28150,12 +28505,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -28257,12 +28612,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -28297,7 +28652,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_784</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -28307,12 +28662,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -28414,12 +28769,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module, Statement, HIERARCHY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -28454,7 +28809,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_785</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -28464,12 +28819,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -28571,12 +28926,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module, Statement, HIERARCHY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -28611,7 +28966,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_785</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -28621,12 +28976,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -28728,12 +29083,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -28768,7 +29123,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_798</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -28778,12 +29133,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -28885,12 +29240,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -28925,7 +29280,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_802</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -28935,12 +29290,12 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -29042,12 +29397,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -29082,7 +29437,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_799</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -29092,12 +29447,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -29199,12 +29554,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -29239,7 +29594,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_800</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -29249,12 +29604,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -29356,12 +29711,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -29396,7 +29751,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_801</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -29406,12 +29761,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -29513,12 +29868,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -29553,7 +29908,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_803</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -29563,12 +29918,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -29670,12 +30025,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -29710,7 +30065,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_772</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -29720,12 +30075,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -29827,12 +30182,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -29867,7 +30222,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_773</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -29877,12 +30232,12 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -29984,12 +30339,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -30024,7 +30379,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_774</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -30034,12 +30389,12 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -30141,12 +30496,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -30181,7 +30536,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_775</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -30191,12 +30546,12 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -30298,12 +30653,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -30338,7 +30693,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_776</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -30348,12 +30703,12 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -30455,12 +30810,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -30495,7 +30850,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_777</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -30505,12 +30860,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -30612,12 +30967,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -30652,7 +31007,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_778</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -30662,12 +31017,12 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -30769,12 +31124,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -30809,7 +31164,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_779</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -30819,12 +31174,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -30926,12 +31281,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -30966,7 +31321,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_780</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -30976,12 +31331,12 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -31083,12 +31438,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -31123,7 +31478,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_806</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -31133,12 +31488,12 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -31240,12 +31595,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -31280,7 +31635,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_807</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -31290,12 +31645,12 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -31397,12 +31752,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -31437,7 +31792,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_816</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -31447,12 +31802,12 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -31554,12 +31909,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -31594,7 +31949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_817</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -31604,12 +31959,12 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -31711,12 +32066,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -31751,7 +32106,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_818</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -31761,12 +32116,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -31868,12 +32223,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -31908,7 +32263,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_819</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -31918,12 +32273,12 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -32025,12 +32380,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -32065,7 +32420,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_820</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -32075,12 +32430,12 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
@@ -32182,12 +32537,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -32222,7 +32577,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_821</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -32232,12 +32587,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -32339,12 +32694,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -32379,7 +32734,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_822</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -32389,12 +32744,12 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -32496,12 +32851,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -32536,7 +32891,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_823</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -32546,12 +32901,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -32653,12 +33008,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -32693,7 +33048,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_824</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -32703,12 +33058,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -32810,12 +33165,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -32850,7 +33205,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_826</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -32860,12 +33215,12 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -32967,12 +33322,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -33007,7 +33362,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_827</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -33017,12 +33372,12 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -33124,12 +33479,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -33164,7 +33519,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_828</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -33174,12 +33529,12 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -33281,12 +33636,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -33321,7 +33676,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_829</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -33331,12 +33686,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -33438,12 +33793,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -33478,7 +33833,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_825</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -33488,12 +33843,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -33595,12 +33950,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -33635,7 +33990,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_839</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -33645,12 +34000,12 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -33752,12 +34107,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -33792,7 +34147,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_840</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -33802,12 +34157,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -33909,12 +34264,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -33949,7 +34304,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_841</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -33959,12 +34314,12 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
@@ -34066,12 +34421,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -34106,7 +34461,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_835</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -34116,12 +34471,12 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -34223,12 +34578,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -34263,7 +34618,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_836</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -34273,12 +34628,12 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -34380,12 +34735,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">FIELDS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -34420,7 +34775,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_837</t>
+          <t xml:space="preserve">W164a_808</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -34430,12 +34785,12 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">pnson</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">

--- a/LINT/outputs/lint_review.xlsx
+++ b/LINT/outputs/lint_review.xlsx
@@ -262,165 +262,47 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
-    <comment ref="M2" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 32 issues.
-Shared issue IDs: DeadCode-ML_e84cae0edf25, DeadCode-ML_7fbcfb987ea2, DeadCode-ML_4061be3b213d, DeadCode-ML_37ccad7cafff, DeadCode-ML_5355615cf12e, DeadCode-ML_f4b3854a503a, DeadCode-ML_515337bfea90, DeadCode-ML_097ffa5f22ec, DeadCode-ML_51ab66d6b498, DeadCode-ML_14a921a01cb4, DeadCode-ML_6817476ffd8b, DeadCode-ML_1763cba8fabb, DeadCode-ML_4eb385741c5b, DeadCode-ML_fcc27bcb35f3, DeadCode-ML_9f84acebc779, DeadCode-ML_320417ba96fc, DeadCode-ML_8a1be6df56cf, DeadCode-ML_3f40c134f801, DeadCode-ML_520b0d4a7048, DeadCode-ML_fbb63c7ca9b7, DeadCode-ML_164f1d6db727, DeadCode-ML_323fbdc90de8, DeadCode-ML_75c765148170, DeadCode-ML_989754a375df, DeadCode-ML_c811eb95211b, DeadCode-ML_a870b15ab72f, DeadCode-ML_e22b6a54e417, DeadCode-ML_28eef1dad7ca, DeadCode-ML_366797be4f73, DeadCode-ML_c2740f9a65ca, DeadCode-ML_d48f18b9af6a</t>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
     <comment ref="M4" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+        <t xml:space="preserve">Primary waiver rule shared by 4 issues.
+Shared issue IDs: DeadCode-ML_4061be3b213d, DeadCode-ML_37ccad7cafff, DeadCode-ML_5355615cf12e</t>
       </text>
     </comment>
     <comment ref="M5" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_741 with primary issue DeadCode-ML_7fbcfb987ea2.</t>
       </text>
     </comment>
     <comment ref="M6" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_741 with primary issue DeadCode-ML_7fbcfb987ea2.</t>
       </text>
     </comment>
     <comment ref="M7" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M8" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M9" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M10" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_741 with primary issue DeadCode-ML_7fbcfb987ea2.</t>
       </text>
     </comment>
     <comment ref="M11" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
+Shared issue IDs: DeadCode-ML_14a921a01cb4</t>
       </text>
     </comment>
     <comment ref="M12" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M13" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M14" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M15" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M16" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M17" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M18" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M19" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M20" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M21" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M22" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M23" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M24" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M25" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M26" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M27" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M28" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M29" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_748 with primary issue DeadCode-ML_51ab66d6b498.</t>
       </text>
     </comment>
     <comment ref="M30" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
+Shared issue IDs: DeadCode-ML_366797be4f73</t>
       </text>
     </comment>
     <comment ref="M31" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M32" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
-      </text>
-    </comment>
-    <comment ref="M33" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_739 with primary issue DeadCode-ML_3a66f0d939c6.</t>
+        <t xml:space="preserve">Shares waiver rule DeadCode-ML_767 with primary issue DeadCode-ML_28eef1dad7ca.</t>
       </text>
     </comment>
   </commentList>
@@ -666,281 +548,37 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
-    <comment ref="M2" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 52 issues.
-Shared issue IDs: W164a_fd6a370a79ab, W164a_d93541370b31, W164a_7660b53e6188, W164a_c90a63b2d9e8, W164a_1d457f0d51fe, W164a_c078e63cfa3e, W164a_b1c30aa3f537, W164a_b16c35b5e10c, W164a_017526ab4c3d, W164a_c505e9870872, W164a_97e34627177b, W164a_b105ea5a36d7, W164a_af9f5f624f8c, W164a_1064ea20e23f, W164a_d33034023f51, W164a_8efcf1475d55, W164a_043a813ca8f6, W164a_72d36f1914f2, W164a_e97c355c8578, W164a_8ae0b89979a0, W164a_4f28e5ce8f80, W164a_2cf4a06f09c5, W164a_5e0b6dc4ac33, W164a_4e84e698ed3e, W164a_a0c63c9da2e6, W164a_6fc4541b3f0d, W164a_453183e95577, W164a_4a2e5e0663a5, W164a_6ff437a3ada4, W164a_161793cb7dad, W164a_ebd65b48e89f, W164a_dc52da86c0c0, W164a_6fda0611280a, W164a_ea91e32f9aa7, W164a_ccf02468d9ed, W164a_6baf6e5ad83d, W164a_ad7c6281ae5d, W164a_4f36dd084a7e, W164a_fcad9e726414, W164a_f08d25377633, W164a_fe2225ff642e, W164a_33135cff7657, W164a_d681159d5355, W164a_d4ea1a544292, W164a_911d84fd734b, W164a_c236385e4a5a, W164a_87f654826bb3, W164a_f0e03f5a7b78, W164a_25c7ecc3014c, W164a_f4629a2c0a13, W164a_40e2f3cc3783</t>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M4" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M5" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M6" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
     <comment ref="M7" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
+Shared issue IDs: W164a_c078e63cfa3e</t>
       </text>
     </comment>
     <comment ref="M8" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M9" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M10" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M11" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M12" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M14" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 3 issues.
-Shared issue IDs: W164a_f303846eddbf, W164a_1ab2b57028bc</t>
+        <t xml:space="preserve">Shares waiver rule W164a_811 with primary issue W164a_1d457f0d51fe.</t>
       </text>
     </comment>
     <comment ref="M15" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
+Shared issue IDs: W164a_b105ea5a36d7</t>
       </text>
     </comment>
     <comment ref="M16" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M17" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M18" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+        <t xml:space="preserve">Shares waiver rule W164a_793 with primary issue W164a_97e34627177b.</t>
       </text>
     </comment>
     <comment ref="M19" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule W164a_792 with primary issue W164a_411e166bb6e8.</t>
+        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
+Shared issue IDs: W164a_1ab2b57028bc</t>
       </text>
     </comment>
     <comment ref="M20" authorId="0">
       <text>
-        <t xml:space="preserve">Shares waiver rule W164a_792 with primary issue W164a_411e166bb6e8.</t>
-      </text>
-    </comment>
-    <comment ref="M21" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M22" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M23" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M24" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M25" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M26" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M27" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M28" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M29" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M30" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M31" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M32" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M33" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M34" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M35" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M36" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M37" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M38" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M39" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M40" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M41" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M42" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M43" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M44" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M45" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M46" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M47" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M48" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M49" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M50" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M51" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M52" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M53" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M54" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M55" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M56" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
-      </text>
-    </comment>
-    <comment ref="M57" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_808 with primary issue W164a_aa9901c77213.</t>
+        <t xml:space="preserve">Shares waiver rule W164a_785 with primary issue W164a_f303846eddbf.</t>
       </text>
     </comment>
   </commentList>
@@ -2098,7 +1736,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2108,7 +1746,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2245,7 +1883,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2255,7 +1893,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -2392,7 +2030,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -2402,7 +2040,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2733,7 +2371,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -2743,7 +2381,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2875,7 +2513,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2885,7 +2523,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -3017,7 +2655,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -3027,7 +2665,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -3159,7 +2797,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -3169,7 +2807,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -3301,7 +2939,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -3311,7 +2949,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -3443,7 +3081,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -3453,7 +3091,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -3585,7 +3223,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -3595,7 +3233,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -3727,7 +3365,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -3737,7 +3375,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -3777,7 +3415,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t xml:space="preserve">       .O_EMPTY_CNT ( w_regfifo_empty_cnt    ),</t>
+          <t xml:space="preserve">       .O_EMPTY_CNT ( w_regfifo_empty_cnt    ), </t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3869,7 +3507,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -3879,7 +3517,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -3919,7 +3557,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t xml:space="preserve">       .O_FULL_CNT  ( w_regfifo_full_cnt     )</t>
+          <t xml:space="preserve">       .O_FULL_CNT  ( w_regfifo_full_cnt     )  </t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -4011,7 +3649,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -4021,7 +3659,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -4153,7 +3791,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -4163,7 +3801,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -4295,7 +3933,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -4305,7 +3943,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -4437,7 +4075,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -4447,7 +4085,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -4579,7 +4217,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -4589,7 +4227,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -4721,7 +4359,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -4731,7 +4369,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -4863,7 +4501,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4873,7 +4511,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -5005,7 +4643,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -5015,7 +4653,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -5147,7 +4785,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -5157,7 +4795,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -5289,7 +4927,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -5299,7 +4937,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -5431,7 +5069,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -5441,7 +5079,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -5573,7 +5211,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5583,7 +5221,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5715,7 +5353,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -5725,7 +5363,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -5857,7 +5495,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -5867,7 +5505,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -5999,7 +5637,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -6009,7 +5647,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -6141,7 +5779,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -6151,7 +5789,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -6283,7 +5921,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -6293,7 +5931,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -6425,7 +6063,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -6435,7 +6073,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -6567,7 +6205,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -6577,7 +6215,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -6709,7 +6347,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -6719,7 +6357,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -6851,7 +6489,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -6861,7 +6499,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -6993,7 +6631,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -7003,7 +6641,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -7135,7 +6773,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -7145,7 +6783,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -7277,7 +6915,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -7287,7 +6925,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -7419,7 +7057,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -7429,7 +7067,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -7561,7 +7199,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -7571,7 +7209,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -7703,7 +7341,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -7713,7 +7351,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -7845,7 +7483,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -7855,7 +7493,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -7987,7 +7625,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -7997,7 +7635,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -8129,7 +7767,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -8139,7 +7777,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -8271,7 +7909,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -8281,7 +7919,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -8413,7 +8051,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -8423,7 +8061,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -8555,7 +8193,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -8565,7 +8203,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -8697,7 +8335,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -8707,7 +8345,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -8839,7 +8477,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -8849,7 +8487,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -8981,7 +8619,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -8991,7 +8629,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -9123,7 +8761,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -9133,7 +8771,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -9265,7 +8903,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -9275,7 +8913,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -9407,7 +9045,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -9417,7 +9055,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -9549,7 +9187,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -9559,7 +9197,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -9691,7 +9329,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -9701,7 +9339,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -9833,7 +9471,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -9843,7 +9481,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -9975,7 +9613,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -9985,7 +9623,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -10117,7 +9755,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -10127,7 +9765,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -10259,7 +9897,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -10269,7 +9907,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -10401,7 +10039,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -10411,7 +10049,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -10543,7 +10181,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -10553,7 +10191,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -10685,7 +10323,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -10695,7 +10333,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -10827,7 +10465,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -10837,7 +10475,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -10969,7 +10607,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -10979,7 +10617,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -11111,7 +10749,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -11121,7 +10759,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -11253,7 +10891,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -11263,7 +10901,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -11395,7 +11033,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -11405,7 +11043,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -11537,7 +11175,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -11547,7 +11185,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -11679,7 +11317,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -11689,7 +11327,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -11821,7 +11459,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -11831,7 +11469,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -11963,7 +11601,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -11973,7 +11611,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -12105,7 +11743,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -12115,7 +11753,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -12247,7 +11885,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -12257,7 +11895,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -12389,7 +12027,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -12399,7 +12037,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -12531,7 +12169,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -12541,7 +12179,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -12673,7 +12311,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -12683,7 +12321,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -12815,7 +12453,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -12825,7 +12463,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -12957,7 +12595,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -12967,7 +12605,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -13099,7 +12737,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -13109,7 +12747,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -13241,7 +12879,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -13251,7 +12889,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -13383,7 +13021,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -13393,7 +13031,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -13525,7 +13163,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -13535,7 +13173,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -13667,7 +13305,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -13677,7 +13315,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -13809,7 +13447,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -13819,7 +13457,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -13951,7 +13589,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -13961,7 +13599,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -14093,7 +13731,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -14103,7 +13741,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -14235,7 +13873,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -14245,7 +13883,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -14377,7 +14015,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -14387,7 +14025,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -14519,7 +14157,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -14529,7 +14167,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -14661,7 +14299,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -14671,7 +14309,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -14803,7 +14441,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -14813,7 +14451,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -14945,7 +14583,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -14955,7 +14593,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -15087,7 +14725,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -15097,7 +14735,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -15229,7 +14867,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -15239,7 +14877,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -15371,7 +15009,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -15381,7 +15019,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -15513,7 +15151,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -15523,7 +15161,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -15655,7 +15293,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -15665,7 +15303,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -15797,7 +15435,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -15807,7 +15445,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -15939,7 +15577,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -15949,7 +15587,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -16081,7 +15719,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -16091,7 +15729,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -16223,7 +15861,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -16233,7 +15871,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -16365,7 +16003,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -16375,7 +16013,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -16507,7 +16145,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -16517,7 +16155,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -16649,7 +16287,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -16659,7 +16297,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -16791,7 +16429,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -16801,7 +16439,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -16933,7 +16571,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -16943,7 +16581,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -17075,7 +16713,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -17085,7 +16723,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -17217,7 +16855,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -17227,7 +16865,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -17359,7 +16997,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -17369,7 +17007,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -17501,7 +17139,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -17511,7 +17149,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -17643,7 +17281,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -17653,7 +17291,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -17785,7 +17423,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -17795,7 +17433,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -17927,7 +17565,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -17937,7 +17575,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -18069,7 +17707,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -18079,7 +17717,7 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -18211,7 +17849,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -18221,7 +17859,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -18353,7 +17991,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -18363,7 +18001,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -18495,7 +18133,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -18505,7 +18143,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -18637,7 +18275,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -18647,7 +18285,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -18779,7 +18417,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -18789,7 +18427,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -18921,7 +18559,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -18931,7 +18569,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -19063,7 +18701,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -19073,7 +18711,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -19335,12 +18973,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19385,7 +19023,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -19395,7 +19033,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -19713,12 +19351,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19763,7 +19401,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -19773,7 +19411,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -19850,12 +19488,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19890,7 +19528,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -19900,7 +19538,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -19910,7 +19548,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -19987,12 +19625,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20027,7 +19665,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_741</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -20037,7 +19675,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -20047,7 +19685,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -20124,12 +19762,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20164,7 +19802,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_741</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -20174,7 +19812,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -20184,7 +19822,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -20261,12 +19899,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20301,7 +19939,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_741</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -20311,7 +19949,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -20321,7 +19959,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -20398,12 +20036,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20438,7 +20076,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_741</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -20448,7 +20086,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -20458,7 +20096,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -20535,12 +20173,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20575,7 +20213,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_745</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -20585,7 +20223,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -20595,7 +20233,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -20672,12 +20310,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20712,7 +20350,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_746</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -20722,7 +20360,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -20732,7 +20370,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -20809,12 +20447,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20849,7 +20487,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_747</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -20859,7 +20497,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -20869,7 +20507,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -20946,12 +20584,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20986,7 +20624,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_748</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -20996,7 +20634,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -21006,7 +20644,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -21083,12 +20721,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21123,7 +20761,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_748</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -21133,7 +20771,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -21143,7 +20781,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -21220,12 +20858,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21260,7 +20898,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_750</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -21270,7 +20908,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -21280,7 +20918,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -21357,12 +20995,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -21397,7 +21035,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_763</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -21407,7 +21045,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -21417,7 +21055,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -21494,12 +21132,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -21534,7 +21172,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_764</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -21544,7 +21182,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -21554,7 +21192,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -21631,12 +21269,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -21671,7 +21309,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_765</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -21681,7 +21319,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -21691,7 +21329,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -21768,12 +21406,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -21808,7 +21446,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_766</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -21818,7 +21456,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -21828,7 +21466,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -21905,12 +21543,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -21945,7 +21583,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_751</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -21955,7 +21593,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -21965,7 +21603,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -22042,12 +21680,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -22082,7 +21720,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_752</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -22092,7 +21730,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -22102,7 +21740,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -22179,12 +21817,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -22219,7 +21857,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_753</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -22229,7 +21867,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -22239,7 +21877,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -22316,12 +21954,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -22356,7 +21994,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_754</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -22366,7 +22004,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -22376,7 +22014,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -22453,12 +22091,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -22493,7 +22131,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_755</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -22503,7 +22141,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -22513,7 +22151,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -22590,12 +22228,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -22630,7 +22268,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_756</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -22640,7 +22278,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -22650,7 +22288,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -22727,12 +22365,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -22767,7 +22405,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_757</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -22777,7 +22415,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -22787,7 +22425,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -22864,12 +22502,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -22904,7 +22542,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_758</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -22914,7 +22552,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -22924,7 +22562,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -23001,12 +22639,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -23041,7 +22679,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_759</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -23051,7 +22689,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -23061,7 +22699,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -23138,12 +22776,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -23178,7 +22816,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_760</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -23188,7 +22826,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -23198,7 +22836,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -23275,12 +22913,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -23315,7 +22953,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_761</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -23325,7 +22963,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -23335,7 +22973,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -23412,12 +23050,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -23452,7 +23090,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_762</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -23462,7 +23100,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -23472,7 +23110,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -23549,12 +23187,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -23589,7 +23227,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_767</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -23599,7 +23237,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -23609,7 +23247,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -23686,12 +23324,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -23726,7 +23364,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_767</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -23736,7 +23374,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -23746,7 +23384,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -23823,12 +23461,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -23863,7 +23501,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_769</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -23873,7 +23511,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -23883,7 +23521,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -23960,12 +23598,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_DATAGEN</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -24000,7 +23638,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_770</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -24010,7 +23648,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -24020,7 +23658,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -24345,7 +23983,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -24355,7 +23993,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -24492,7 +24130,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -24502,7 +24140,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -24639,7 +24277,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -24649,7 +24287,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -24978,7 +24616,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -24988,7 +24626,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -25120,7 +24758,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -25130,7 +24768,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -25262,7 +24900,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -25272,7 +24910,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -25404,7 +25042,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -25414,7 +25052,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -25738,7 +25376,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -25748,7 +25386,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -25880,7 +25518,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -25890,7 +25528,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -26022,7 +25660,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -26032,7 +25670,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -26164,7 +25802,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -26174,7 +25812,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -26306,7 +25944,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -26316,7 +25954,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -26448,7 +26086,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -26458,7 +26096,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -26590,7 +26228,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -26600,7 +26238,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -26898,12 +26536,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -26948,7 +26586,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -26958,7 +26596,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -26998,7 +26636,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    assign nxt_r_cnt = (r_cnt == FIFO_DEPTH-1) ? ({AW{1'b0}}) : (r_cnt + 1'b1);</t>
+          <t xml:space="preserve">    assign nxt_r_cnt = (r_cnt == FIFO_DEPTH-1) ? ({AW{1'b0}}) : (r_cnt + 1'b1); </t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -27060,12 +26698,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -27100,7 +26738,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_809</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -27110,7 +26748,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -27120,7 +26758,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -27160,7 +26798,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    assign nxt_w_cnt = (w_cnt == FIFO_DEPTH-1) ? ({AW{1'b0}}) : (w_cnt + 1'b1);</t>
+          <t xml:space="preserve">    assign nxt_w_cnt = (w_cnt == FIFO_DEPTH-1) ? ({AW{1'b0}}) : (w_cnt + 1'b1);      </t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -27222,12 +26860,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -27262,7 +26900,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_814</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -27272,7 +26910,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -27282,7 +26920,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -27384,12 +27022,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -27424,7 +27062,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_810</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -27434,7 +27072,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -27444,7 +27082,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -27546,12 +27184,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -27586,7 +27224,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_813</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -27596,7 +27234,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -27606,7 +27244,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -27646,7 +27284,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    assign alu_out_val[k*32 +: 32] = (I_DMA_OP_SEL == DATAGEN_OP_ADD)  ? w_alu_op0_val_mux[k*32 +: 32] + I_ALU_OP1_VAL_mux[k*32 +: 32] :</t>
+          <t xml:space="preserve">    assign alu_out_val[k*32 +: 32] = (I_DMA_OP_SEL == DATAGEN_OP_ADD)  ? w_alu_op0_val_mux[k*32 +: 32] + I_ALU_OP1_VAL_mux[k*32 +: 32] : </t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -27708,12 +27346,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -27748,7 +27386,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_811</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -27758,7 +27396,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -27768,7 +27406,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -27808,7 +27446,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t xml:space="preserve">            next_datagen_data[i*32 +: 32] = r_datagen_data[i*32 +: 32] + I_ALU_OP1_VAL[i*32 +: 32];</t>
+          <t xml:space="preserve">            next_datagen_data[i*32 +: 32] = r_datagen_data[i*32 +: 32] + I_ALU_OP1_VAL[i*32 +: 32]; </t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -27870,12 +27508,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -27910,7 +27548,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_811</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -27920,7 +27558,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -27930,7 +27568,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -27970,7 +27608,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t xml:space="preserve">            next_datagen_data[i*32 +: 32] = r_datagen_data[i*32 +: 32] + I_ALU_OP1_VAL[i*32 +: 32];</t>
+          <t xml:space="preserve">            next_datagen_data[i*32 +: 32] = r_datagen_data[i*32 +: 32] + I_ALU_OP1_VAL[i*32 +: 32]; </t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -28032,12 +27670,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -28072,7 +27710,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_781</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -28082,7 +27720,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -28092,7 +27730,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -28194,12 +27832,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -28234,7 +27872,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_815</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -28244,7 +27882,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -28254,7 +27892,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -28356,12 +27994,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -28396,7 +28034,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_789</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -28406,7 +28044,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -28416,7 +28054,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -28518,12 +28156,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -28558,7 +28196,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_790</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -28568,7 +28206,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -28578,7 +28216,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -28680,12 +28318,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -28730,7 +28368,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -28740,7 +28378,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -28842,12 +28480,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -28892,7 +28530,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -28902,7 +28540,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -29004,12 +28642,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -29044,7 +28682,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_793</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -29054,7 +28692,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -29064,7 +28702,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -29166,12 +28804,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -29206,7 +28844,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_793</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -29216,7 +28854,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -29226,7 +28864,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -29328,12 +28966,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -29368,7 +29006,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_783</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -29378,7 +29016,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -29388,7 +29026,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -29490,12 +29128,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -29530,7 +29168,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_784</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -29540,7 +29178,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -29550,7 +29188,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -29652,12 +29290,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module, Statement, HIERARCHY</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -29692,7 +29330,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_792</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -29702,7 +29340,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -29712,7 +29350,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -29814,12 +29452,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module, Statement, HIERARCHY</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -29854,7 +29492,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_792</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -29864,7 +29502,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -29874,7 +29512,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -29976,12 +29614,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -30016,7 +29654,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_798</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -30026,7 +29664,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -30036,7 +29674,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -30138,12 +29776,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -30178,7 +29816,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_802</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -30188,7 +29826,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -30198,7 +29836,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -30300,12 +29938,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -30340,7 +29978,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_799</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -30350,7 +29988,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -30360,7 +29998,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -30462,12 +30100,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -30502,7 +30140,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_800</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -30512,7 +30150,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -30522,7 +30160,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -30624,12 +30262,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -30664,7 +30302,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_801</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -30674,7 +30312,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -30684,7 +30322,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -30786,12 +30424,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -30826,7 +30464,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_803</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -30836,7 +30474,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -30846,7 +30484,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -30886,7 +30524,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    assign nxt_w_cnt = (w_cnt == FIFO_DEPTH-1) ? ({AW{1'b0}}) : (w_cnt + 1'b1);</t>
+          <t xml:space="preserve">    assign nxt_w_cnt = (w_cnt == FIFO_DEPTH-1) ? ({AW{1'b0}}) : (w_cnt + 1'b1);      </t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -30948,12 +30586,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -30988,7 +30626,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_772</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -30998,7 +30636,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -31008,7 +30646,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -31110,12 +30748,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -31150,7 +30788,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_773</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -31160,7 +30798,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -31170,7 +30808,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -31272,12 +30910,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -31312,7 +30950,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_774</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -31322,7 +30960,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -31332,7 +30970,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -31434,12 +31072,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -31474,7 +31112,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_775</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -31484,7 +31122,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -31494,7 +31132,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -31596,12 +31234,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -31636,7 +31274,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_776</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -31646,7 +31284,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -31656,7 +31294,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -31758,12 +31396,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -31798,7 +31436,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_777</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -31808,7 +31446,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -31818,7 +31456,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -31920,12 +31558,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -31960,7 +31598,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_778</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -31970,7 +31608,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -31980,7 +31618,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -32082,12 +31720,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -32122,7 +31760,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_779</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -32132,7 +31770,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -32142,7 +31780,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -32244,12 +31882,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -32284,7 +31922,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_780</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -32294,7 +31932,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -32304,7 +31942,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -32406,12 +32044,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -32446,7 +32084,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_806</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -32456,7 +32094,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -32466,7 +32104,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -32568,12 +32206,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -32608,7 +32246,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_807</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -32618,7 +32256,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -32628,7 +32266,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -32730,12 +32368,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -32770,7 +32408,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_816</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -32780,7 +32418,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -32790,7 +32428,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -32892,12 +32530,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -32932,7 +32570,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_817</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -32942,7 +32580,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -32952,7 +32590,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -33054,12 +32692,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -33094,7 +32732,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_818</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -33104,7 +32742,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -33114,7 +32752,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -33216,12 +32854,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -33256,7 +32894,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_819</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -33266,7 +32904,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -33276,7 +32914,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -33378,12 +33016,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -33418,7 +33056,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_820</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -33428,7 +33066,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -33438,7 +33076,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -33540,12 +33178,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -33580,7 +33218,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_821</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -33590,7 +33228,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -33600,7 +33238,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -33702,12 +33340,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -33742,7 +33380,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_822</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -33752,7 +33390,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -33762,7 +33400,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -33864,12 +33502,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -33904,7 +33542,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_823</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -33914,7 +33552,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -33924,7 +33562,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -34026,12 +33664,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -34066,7 +33704,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_824</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -34076,7 +33714,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -34086,7 +33724,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -34188,12 +33826,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -34228,7 +33866,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_826</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -34238,7 +33876,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -34248,7 +33886,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -34350,12 +33988,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -34390,7 +34028,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_827</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -34400,7 +34038,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -34410,7 +34048,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -34512,12 +34150,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -34552,7 +34190,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_828</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -34562,7 +34200,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -34572,7 +34210,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -34674,12 +34312,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -34714,7 +34352,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_829</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -34724,7 +34362,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -34734,7 +34372,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -34836,12 +34474,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -34876,7 +34514,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_825</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -34886,7 +34524,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -34896,7 +34534,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -34998,12 +34636,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -35038,7 +34676,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_839</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -35048,7 +34686,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -35058,7 +34696,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -35160,12 +34798,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -35200,7 +34838,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_840</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -35210,7 +34848,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -35220,7 +34858,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -35322,12 +34960,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -35362,7 +35000,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_841</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -35372,7 +35010,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -35382,7 +35020,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -35484,12 +35122,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -35524,7 +35162,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_835</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -35534,7 +35172,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -35544,7 +35182,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -35646,12 +35284,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -35686,7 +35324,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_836</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -35696,7 +35334,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -35706,7 +35344,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -35808,12 +35446,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">FIELDS</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Goal, Module=AESDMA_RD_DESC, Statement=n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;, HIERARCHY=:BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -35848,7 +35486,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_837</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -35858,7 +35496,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -35868,7 +35506,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -36206,7 +35844,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -36216,7 +35854,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -36343,7 +35981,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -36353,7 +35991,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -36480,7 +36118,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -36490,7 +36128,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -36617,7 +36255,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -36627,7 +36265,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -36754,7 +36392,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -36764,7 +36402,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -36891,7 +36529,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -36901,7 +36539,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -37028,7 +36666,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -37038,7 +36676,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -37165,7 +36803,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -37175,7 +36813,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -37302,7 +36940,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -37312,7 +36950,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -37439,7 +37077,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -37449,7 +37087,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -37489,7 +37127,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    input                               I_RdDesc_Busy,</t>
+          <t xml:space="preserve">    input                               I_RdDesc_Busy, </t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -37576,7 +37214,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -37586,7 +37224,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -37713,7 +37351,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -37723,7 +37361,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -37850,7 +37488,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -37860,7 +37498,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -37987,7 +37625,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -37997,7 +37635,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -38124,7 +37762,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -38134,7 +37772,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -38261,7 +37899,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -38271,7 +37909,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -38398,7 +38036,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -38408,7 +38046,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -38535,7 +38173,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -38545,7 +38183,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -38585,7 +38223,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    input  wire     [  pBwParDt-1:00]   AXI_MI0_RDATA_PARITY                ,</t>
+          <t xml:space="preserve">    input  wire     [  pBwParDt-1:00]   AXI_MI0_RDATA_PARITY                ,      </t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -38672,7 +38310,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -38682,7 +38320,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -38989,7 +38627,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -38999,7 +38637,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -39121,7 +38759,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -39131,7 +38769,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -39253,7 +38891,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -39263,7 +38901,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -39385,7 +39023,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -39395,7 +39033,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -39517,7 +39155,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -39527,7 +39165,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -39649,7 +39287,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -39659,7 +39297,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -39781,7 +39419,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -39791,7 +39429,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -39913,7 +39551,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -39923,7 +39561,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -40045,7 +39683,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -40055,7 +39693,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -40177,7 +39815,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -40187,7 +39825,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -40309,7 +39947,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -40319,7 +39957,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -40441,7 +40079,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -40451,7 +40089,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -40573,7 +40211,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -40583,7 +40221,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -40705,7 +40343,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -40715,7 +40353,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -40755,7 +40393,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   .O_FULL_CNT  ( )//w_regfifo_full_cnt     )</t>
+          <t xml:space="preserve">   .O_FULL_CNT  ( )//w_regfifo_full_cnt     ) </t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -40837,7 +40475,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -40847,7 +40485,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -40969,7 +40607,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -40979,7 +40617,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -41101,7 +40739,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -41111,7 +40749,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -41233,7 +40871,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -41243,7 +40881,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -41365,7 +41003,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -41375,7 +41013,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -41415,7 +41053,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t xml:space="preserve">   .O_FULL_CNT  (                        )</t>
+          <t xml:space="preserve">   .O_FULL_CNT  (                        ) </t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -41497,7 +41135,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -41507,7 +41145,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -41629,7 +41267,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -41639,7 +41277,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -41761,7 +41399,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -41771,7 +41409,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -41893,7 +41531,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -41903,7 +41541,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -42025,7 +41663,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -42035,7 +41673,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -42157,7 +41795,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -42167,7 +41805,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -42289,7 +41927,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -42299,7 +41937,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -42421,7 +42059,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -42431,7 +42069,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -42553,7 +42191,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -42563,7 +42201,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -42685,7 +42323,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -42695,7 +42333,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -42817,7 +42455,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -42827,7 +42465,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -42949,7 +42587,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -42959,7 +42597,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -43081,7 +42719,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -43091,7 +42729,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -43213,7 +42851,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -43223,7 +42861,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -43345,7 +42983,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -43355,7 +42993,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -43477,7 +43115,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -43487,7 +43125,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -43609,7 +43247,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -43619,7 +43257,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -43741,7 +43379,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -43751,7 +43389,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -43873,7 +43511,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -43883,7 +43521,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -44005,7 +43643,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -44015,7 +43653,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -44137,7 +43775,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -44147,7 +43785,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -44269,7 +43907,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -44279,7 +43917,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -44401,7 +44039,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -44411,7 +44049,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -44533,7 +44171,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -44543,7 +44181,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -44665,7 +44303,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -44675,7 +44313,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -44797,7 +44435,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -44807,7 +44445,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -44929,7 +44567,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -44939,7 +44577,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -45061,7 +44699,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -45071,7 +44709,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -45193,7 +44831,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -45203,7 +44841,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -45325,7 +44963,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -45335,7 +44973,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -45457,7 +45095,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -45467,7 +45105,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -45589,7 +45227,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -45599,7 +45237,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -45721,7 +45359,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -45731,7 +45369,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -45853,7 +45491,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -45863,7 +45501,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -45985,7 +45623,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -45995,7 +45633,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -46327,7 +45965,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -46337,7 +45975,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -46484,7 +46122,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -46494,7 +46132,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -46641,7 +46279,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">vc_waiver.tcl</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -46651,7 +46289,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-09-2026 11:00:21</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">

--- a/LINT/outputs/lint_review.xlsx
+++ b/LINT/outputs/lint_review.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Tree Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="DeadCode-ML" sheetId="2" r:id="rId2"/>
     <sheet name="MissingFsmStateTransition" sheetId="3" r:id="rId3"/>
     <sheet name="NotReachableFsmState" sheetId="4" r:id="rId4"/>
@@ -17,7 +17,7 @@
     <sheet name="Instructions" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tree Summary'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DeadCode-ML'!$A$1:$AA$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MissingFsmStateTransition'!$A$1:$AC$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'NotReachableFsmState'!$A$1:$AB$5</definedName>
@@ -262,49 +262,6 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
-    <comment ref="M4" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 4 issues.
-Shared issue IDs: DeadCode-ML_4061be3b213d, DeadCode-ML_37ccad7cafff, DeadCode-ML_5355615cf12e</t>
-      </text>
-    </comment>
-    <comment ref="M5" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_741 with primary issue DeadCode-ML_7fbcfb987ea2.</t>
-      </text>
-    </comment>
-    <comment ref="M6" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_741 with primary issue DeadCode-ML_7fbcfb987ea2.</t>
-      </text>
-    </comment>
-    <comment ref="M7" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_741 with primary issue DeadCode-ML_7fbcfb987ea2.</t>
-      </text>
-    </comment>
-    <comment ref="M11" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: DeadCode-ML_14a921a01cb4</t>
-      </text>
-    </comment>
-    <comment ref="M12" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_748 with primary issue DeadCode-ML_51ab66d6b498.</t>
-      </text>
-    </comment>
-    <comment ref="M30" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: DeadCode-ML_366797be4f73</t>
-      </text>
-    </comment>
-    <comment ref="M31" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule DeadCode-ML_767 with primary issue DeadCode-ML_28eef1dad7ca.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -479,17 +436,6 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
-    <comment ref="M2" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: SignedUnsignedExpr-ML_5265491e59fa</t>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule SignedUnsignedExpr-ML_787 with primary issue SignedUnsignedExpr-ML_0718299113f4.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -546,39 +492,6 @@
       <text>
         <t xml:space="preserve">full: the issue comes from report_lint.full
 waived: the issue comes from report_lint.waived</t>
-      </text>
-    </comment>
-    <comment ref="M7" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: W164a_c078e63cfa3e</t>
-      </text>
-    </comment>
-    <comment ref="M8" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_811 with primary issue W164a_1d457f0d51fe.</t>
-      </text>
-    </comment>
-    <comment ref="M15" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: W164a_b105ea5a36d7</t>
-      </text>
-    </comment>
-    <comment ref="M16" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_793 with primary issue W164a_97e34627177b.</t>
-      </text>
-    </comment>
-    <comment ref="M19" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: W164a_1ab2b57028bc</t>
-      </text>
-    </comment>
-    <comment ref="M20" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W164a_785 with primary issue W164a_f303846eddbf.</t>
       </text>
     </comment>
   </commentList>
@@ -697,111 +610,6 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
-    <comment ref="M2" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 5 issues.
-Shared issue IDs: W287b_c85f2a628cf9, W287b_b08b0bfb572f, W287b_4a5057baf3e1, W287b_0ebc6504f858</t>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 5 issues.
-Shared issue IDs: W287b_ccebc644dfd5, W287b_8d49e82f879e, W287b_2858ec565b3e, W287b_0b46201d1428</t>
-      </text>
-    </comment>
-    <comment ref="M4" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1001 with primary issue W287b_ab0b05504edd.</t>
-      </text>
-    </comment>
-    <comment ref="M5" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1002 with primary issue W287b_f9ca9ff10589.</t>
-      </text>
-    </comment>
-    <comment ref="M6" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1001 with primary issue W287b_ab0b05504edd.</t>
-      </text>
-    </comment>
-    <comment ref="M7" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1002 with primary issue W287b_f9ca9ff10589.</t>
-      </text>
-    </comment>
-    <comment ref="M8" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1001 with primary issue W287b_ab0b05504edd.</t>
-      </text>
-    </comment>
-    <comment ref="M9" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1002 with primary issue W287b_f9ca9ff10589.</t>
-      </text>
-    </comment>
-    <comment ref="M10" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1001 with primary issue W287b_ab0b05504edd.</t>
-      </text>
-    </comment>
-    <comment ref="M11" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1002 with primary issue W287b_f9ca9ff10589.</t>
-      </text>
-    </comment>
-    <comment ref="M43" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 2 issues.
-Shared issue IDs: W287b_de35fefdb324</t>
-      </text>
-    </comment>
-    <comment ref="M44" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_860 with primary issue W287b_5d5458e67f67.</t>
-      </text>
-    </comment>
-    <comment ref="M46" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 4 issues.
-Shared issue IDs: W287b_9d47d1b298af, W287b_167aec9fe6b3, W287b_0a639fe92ca6</t>
-      </text>
-    </comment>
-    <comment ref="M47" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1027 with primary issue W287b_2a87793fcb79.</t>
-      </text>
-    </comment>
-    <comment ref="M48" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1027 with primary issue W287b_2a87793fcb79.</t>
-      </text>
-    </comment>
-    <comment ref="M49" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1027 with primary issue W287b_2a87793fcb79.</t>
-      </text>
-    </comment>
-    <comment ref="M51" authorId="0">
-      <text>
-        <t xml:space="preserve">Primary waiver rule shared by 4 issues.
-Shared issue IDs: W287b_1d91f06c2548, W287b_ef162931c320, W287b_d7be575aaff3</t>
-      </text>
-    </comment>
-    <comment ref="M52" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1018 with primary issue W287b_9514157b531c.</t>
-      </text>
-    </comment>
-    <comment ref="M53" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1018 with primary issue W287b_9514157b531c.</t>
-      </text>
-    </comment>
-    <comment ref="M54" authorId="0">
-      <text>
-        <t xml:space="preserve">Shares waiver rule W287b_1018 with primary issue W287b_9514157b531c.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -877,7 +685,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -902,6 +710,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border/>
@@ -909,11 +729,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -928,7 +751,6 @@
     <col min="5" max="5" width="42" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -939,499 +761,439 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage</t>
+          <t xml:space="preserve">Tag</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tag</t>
+          <t xml:space="preserve">Count</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Count</t>
+          <t xml:space="preserve">Waived</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waived</t>
+          <t xml:space="preserve">Unreviewed</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compressed</t>
+          <t xml:space="preserve">Confirmed</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confirmed</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Remaining</t>
+          <t xml:space="preserve">Pending by reviewer</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">DeadCode-ML</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">MissingFsmStateTransition</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NotReachableFsmState</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">SignedUnsignedExpr-ML</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">W164a</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">56</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">info</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">warning</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">W240</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">19</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">W287b</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">54</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">W362</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">W415a</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">info</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">warning</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">W528</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">116</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">W551</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -1448,42 +1210,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">298</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">298</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">298</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:G13"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1602,62 +1362,62 @@
           <t xml:space="preserve">waiver_timestamp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Violation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FileName</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineNumber</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Statement</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Signal</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HIERARCHY</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CulpritLineNumber</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HDL_STATEMENT</t>
         </is>
@@ -1726,7 +1486,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">W415a_796</t>
+          <t xml:space="preserve">W415a_787</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1741,12 +1501,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -1873,7 +1633,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">W415a_797</t>
+          <t xml:space="preserve">W415a_787</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1888,12 +1648,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -2020,7 +1780,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W415a_805</t>
+          <t xml:space="preserve">W415a_787</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2035,12 +1795,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2125,6 +1885,9 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2242,57 +2005,57 @@
           <t xml:space="preserve">waiver_timestamp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Violation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FileName</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineNumber</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Statement</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">VariableName</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ExprSize</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HIERARCHY</t>
         </is>
@@ -2361,7 +2124,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_916</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2376,12 +2139,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -2503,7 +2266,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_913</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2518,12 +2281,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -2645,7 +2408,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_937</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2660,12 +2423,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2787,7 +2550,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_904</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -2802,12 +2565,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -2929,7 +2692,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_921</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2944,12 +2707,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -3071,7 +2834,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_920</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -3086,12 +2849,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -3213,7 +2976,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_924</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -3228,12 +2991,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -3355,7 +3118,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_936</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -3370,12 +3133,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -3497,7 +3260,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_935</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -3512,12 +3275,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -3639,7 +3402,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_871</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -3654,12 +3417,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -3781,7 +3544,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_881</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -3796,12 +3559,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -3923,7 +3686,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_873</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -3938,12 +3701,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -4065,7 +3828,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_899</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -4080,12 +3843,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -4207,7 +3970,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_898</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -4222,12 +3985,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -4349,7 +4112,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_885</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -4364,12 +4127,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -4491,7 +4254,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_897</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -4506,12 +4269,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -4633,7 +4396,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_896</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -4648,12 +4411,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -4775,7 +4538,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_895</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -4790,12 +4553,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -4917,7 +4680,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_901</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -4932,12 +4695,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -5059,7 +4822,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_900</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -5074,12 +4837,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -5201,7 +4964,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_890</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5216,12 +4979,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -5343,7 +5106,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_891</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -5358,12 +5121,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -5485,7 +5248,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_883</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -5500,12 +5263,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -5627,7 +5390,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_882</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -5642,12 +5405,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -5769,7 +5532,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_894</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -5784,12 +5547,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -5911,7 +5674,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_872</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -5926,12 +5689,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -6053,7 +5816,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_884</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -6068,12 +5831,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -6195,7 +5958,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_888</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -6210,12 +5973,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -6337,7 +6100,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_886</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -6352,12 +6115,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -6479,7 +6242,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_875</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -6494,12 +6257,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -6621,7 +6384,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_874</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -6636,12 +6399,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -6763,7 +6526,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_887</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -6778,12 +6541,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -6905,7 +6668,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_877</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -6920,12 +6683,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -7047,7 +6810,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_876</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -7062,12 +6825,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -7189,7 +6952,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_880</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -7204,12 +6967,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -7331,7 +7094,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_878</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -7346,12 +7109,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -7473,7 +7236,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_879</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -7488,12 +7251,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -7615,7 +7378,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_889</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -7630,12 +7393,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -7757,7 +7520,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_893</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -7772,12 +7535,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -7899,7 +7662,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_892</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -7914,12 +7677,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -8041,7 +7804,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_862</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -8056,12 +7819,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -8183,7 +7946,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_934</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -8198,12 +7961,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -8325,7 +8088,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_946</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -8340,12 +8103,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -8467,7 +8230,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_949</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -8482,12 +8245,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -8609,7 +8372,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_948</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -8624,12 +8387,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -8751,7 +8514,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_952</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -8766,12 +8529,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -8893,7 +8656,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_955</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -8908,12 +8671,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -9035,7 +8798,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_958</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -9050,12 +8813,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -9177,7 +8940,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_961</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -9192,12 +8955,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -9319,7 +9082,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_964</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -9334,12 +9097,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -9461,7 +9224,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_967</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -9476,12 +9239,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -9603,7 +9366,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_970</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -9618,12 +9381,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -9745,7 +9508,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_973</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -9760,12 +9523,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -9887,7 +9650,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_976</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -9902,12 +9665,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -10029,7 +9792,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_979</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -10044,12 +9807,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -10171,7 +9934,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_982</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -10186,12 +9949,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -10313,7 +10076,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_985</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -10328,12 +10091,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -10455,7 +10218,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_988</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -10470,12 +10233,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -10597,7 +10360,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_991</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -10612,12 +10375,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -10739,7 +10502,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_994</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -10754,12 +10517,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -10881,7 +10644,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_951</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -10896,12 +10659,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -11023,7 +10786,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_954</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -11038,12 +10801,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -11165,7 +10928,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_957</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -11180,12 +10943,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -11307,7 +11070,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_960</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -11322,12 +11085,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -11449,7 +11212,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_963</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -11464,12 +11227,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -11591,7 +11354,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_966</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -11606,12 +11369,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -11733,7 +11496,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_969</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -11748,12 +11511,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -11875,7 +11638,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_972</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -11890,12 +11653,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -12017,7 +11780,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_975</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -12032,12 +11795,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -12159,7 +11922,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_978</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -12174,12 +11937,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -12301,7 +12064,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_981</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -12316,12 +12079,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -12443,7 +12206,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_984</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -12458,12 +12221,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -12585,7 +12348,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_987</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -12600,12 +12363,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -12727,7 +12490,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_990</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -12742,12 +12505,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -12869,7 +12632,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_993</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -12884,12 +12647,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -13011,7 +12774,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_953</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -13026,12 +12789,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -13153,7 +12916,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_956</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -13168,12 +12931,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -13295,7 +13058,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_959</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -13310,12 +13073,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -13437,7 +13200,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_962</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -13452,12 +13215,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -13579,7 +13342,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_965</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -13594,12 +13357,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -13721,7 +13484,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_968</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -13736,12 +13499,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -13863,7 +13626,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_971</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -13878,12 +13641,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -14005,7 +13768,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_974</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -14020,12 +13783,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -14147,7 +13910,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_977</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -14162,12 +13925,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -14289,7 +14052,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_980</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -14304,12 +14067,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -14431,7 +14194,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_983</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -14446,12 +14209,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -14573,7 +14336,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_986</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -14588,12 +14351,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -14715,7 +14478,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_989</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -14730,12 +14493,12 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -14857,7 +14620,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_992</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -14872,12 +14635,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -14999,7 +14762,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_995</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -15014,12 +14777,12 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -15141,7 +14904,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_996</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -15156,12 +14919,12 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -15283,7 +15046,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_950</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -15298,12 +15061,12 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -15425,7 +15188,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_947</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -15440,12 +15203,12 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -15567,7 +15330,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_854</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -15582,12 +15345,12 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -15709,7 +15472,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_851</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -15724,12 +15487,12 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -15851,7 +15614,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_852</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -15866,12 +15629,12 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -15993,7 +15756,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_853</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -16008,12 +15771,12 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -16135,7 +15898,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_848</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -16150,12 +15913,12 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -16277,7 +16040,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_849</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -16292,12 +16055,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -16419,7 +16182,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_850</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -16434,12 +16197,12 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -16561,7 +16324,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_856</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -16576,12 +16339,12 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -16703,7 +16466,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_846</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -16718,12 +16481,12 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -16845,7 +16608,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_847</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -16860,12 +16623,12 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -16987,7 +16750,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_855</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -17002,12 +16765,12 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R105" t="inlineStr">
@@ -17129,7 +16892,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_857</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -17144,12 +16907,12 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R106" t="inlineStr">
@@ -17271,7 +17034,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_998</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -17286,12 +17049,12 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R107" t="inlineStr">
@@ -17413,7 +17176,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_999</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -17428,12 +17191,12 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R108" t="inlineStr">
@@ -17555,7 +17318,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_997</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -17570,12 +17333,12 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R109" t="inlineStr">
@@ -17697,7 +17460,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_1024</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -17712,12 +17475,12 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R110" t="inlineStr">
@@ -17839,7 +17602,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_1025</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -17854,12 +17617,12 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -17981,7 +17744,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_1026</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -17996,12 +17759,12 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -18123,7 +17886,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_1022</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -18138,12 +17901,12 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R113" t="inlineStr">
@@ -18265,7 +18028,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_1015</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -18280,12 +18043,12 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R114" t="inlineStr">
@@ -18407,7 +18170,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_1016</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -18422,12 +18185,12 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R115" t="inlineStr">
@@ -18549,7 +18312,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_1017</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -18564,12 +18327,12 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -18691,7 +18454,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">W528_1013</t>
+          <t xml:space="preserve">W528_825</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -18706,12 +18469,12 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R117" t="inlineStr">
@@ -18789,6 +18552,9 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -18904,47 +18670,47 @@
           <t xml:space="preserve">waiver_timestamp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Violation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FileName</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineNumber</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Statement</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NodeType</t>
         </is>
@@ -18973,7 +18739,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -18983,7 +18749,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE")</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -19161,6 +18927,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -19277,52 +19046,52 @@
           <t xml:space="preserve">waiver_timestamp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Violation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FileName</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineNumber</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Statement</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HIERARCHY</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineRange</t>
         </is>
@@ -19351,7 +19120,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -19361,7 +19130,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -19391,7 +19160,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_739</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -19488,7 +19257,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -19498,7 +19267,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -19625,7 +19394,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -19635,7 +19404,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -19665,7 +19434,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_741</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -19762,7 +19531,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -19772,7 +19541,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -19802,7 +19571,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_741</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -19899,7 +19668,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -19909,7 +19678,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -19939,7 +19708,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_741</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -20036,7 +19805,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -20046,7 +19815,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -20076,7 +19845,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_741</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -20173,7 +19942,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -20183,7 +19952,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -20213,7 +19982,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_745</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -20310,7 +20079,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -20320,7 +20089,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -20350,7 +20119,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_746</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -20447,7 +20216,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -20457,7 +20226,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -20487,7 +20256,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_747</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -20584,7 +20353,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -20594,7 +20363,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -20624,7 +20393,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_748</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -20721,7 +20490,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -20731,7 +20500,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -20761,7 +20530,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_748</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -20858,7 +20627,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -20868,7 +20637,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -20898,7 +20667,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_750</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -20995,7 +20764,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -21005,7 +20774,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21035,7 +20804,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_763</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -21132,7 +20901,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -21142,7 +20911,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -21172,7 +20941,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_764</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -21269,7 +21038,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -21279,7 +21048,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -21309,7 +21078,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_765</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -21406,7 +21175,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -21416,7 +21185,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -21446,7 +21215,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_766</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -21543,7 +21312,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -21553,7 +21322,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -21583,7 +21352,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_751</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -21680,7 +21449,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -21690,7 +21459,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -21720,7 +21489,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_752</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -21817,7 +21586,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -21827,7 +21596,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -21857,7 +21626,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_753</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -21954,7 +21723,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -21964,7 +21733,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -21994,7 +21763,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_754</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -22091,7 +21860,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -22101,7 +21870,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -22131,7 +21900,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_755</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -22228,7 +21997,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -22238,7 +22007,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -22268,7 +22037,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_756</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -22365,7 +22134,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -22375,7 +22144,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -22405,7 +22174,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_757</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -22502,7 +22271,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -22512,7 +22281,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -22542,7 +22311,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_758</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -22639,7 +22408,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -22649,7 +22418,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -22679,7 +22448,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_759</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -22776,7 +22545,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -22786,7 +22555,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -22816,7 +22585,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_760</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -22913,7 +22682,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -22923,7 +22692,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -22953,7 +22722,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_761</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -23050,7 +22819,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -23060,7 +22829,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -23090,7 +22859,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_762</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -23187,7 +22956,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -23197,7 +22966,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -23227,7 +22996,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_767</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -23324,7 +23093,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -23334,7 +23103,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -23364,7 +23133,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_767</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -23461,7 +23230,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -23471,7 +23240,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -23501,7 +23270,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_769</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -23598,7 +23367,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -23608,7 +23377,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -23638,7 +23407,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">DeadCode-ML_770</t>
+          <t xml:space="preserve">DeadCode-ML_740</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -23731,6 +23500,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -23849,62 +23621,62 @@
           <t xml:space="preserve">waiver_timestamp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Violation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FileName</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineNumber</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Statement</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HIERARCHY</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FsmName</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FromState</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ToState</t>
         </is>
@@ -23973,7 +23745,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MissingFsmStateTransition_733</t>
+          <t xml:space="preserve">MissingFsmStateTransition_719</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -23988,12 +23760,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -24120,7 +23892,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MissingFsmStateTransition_734</t>
+          <t xml:space="preserve">MissingFsmStateTransition_719</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -24135,12 +23907,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -24267,7 +24039,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MissingFsmStateTransition_732</t>
+          <t xml:space="preserve">MissingFsmStateTransition_719</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -24282,12 +24054,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -24370,6 +24142,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -24487,57 +24262,57 @@
           <t xml:space="preserve">waiver_timestamp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Violation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FileName</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineNumber</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Statement</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HIERARCHY</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FsmName</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FsmState</t>
         </is>
@@ -24606,7 +24381,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NotReachableFsmState_735</t>
+          <t xml:space="preserve">NotReachableFsmState_722</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -24621,12 +24396,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -24748,7 +24523,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NotReachableFsmState_736</t>
+          <t xml:space="preserve">NotReachableFsmState_722</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -24763,12 +24538,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -24890,7 +24665,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NotReachableFsmState_737</t>
+          <t xml:space="preserve">NotReachableFsmState_722</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -24905,12 +24680,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -25032,7 +24807,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NotReachableFsmState_738</t>
+          <t xml:space="preserve">NotReachableFsmState_722</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -25047,12 +24822,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -25130,6 +24905,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -25247,57 +25025,57 @@
           <t xml:space="preserve">waiver_timestamp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Violation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FileName</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineNumber</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Statement</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RTL_EXPRESSION</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HdlExp</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HDL_STATEMENT</t>
         </is>
@@ -25366,7 +25144,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SignedUnsignedExpr-ML_787</t>
+          <t xml:space="preserve">SignedUnsignedExpr-ML_799</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -25381,12 +25159,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -25508,7 +25286,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SignedUnsignedExpr-ML_787</t>
+          <t xml:space="preserve">SignedUnsignedExpr-ML_799</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -25523,12 +25301,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -25650,7 +25428,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SignedUnsignedExpr-ML_830</t>
+          <t xml:space="preserve">SignedUnsignedExpr-ML_799</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -25665,12 +25443,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -25792,7 +25570,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">SignedUnsignedExpr-ML_831</t>
+          <t xml:space="preserve">SignedUnsignedExpr-ML_799</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -25807,12 +25585,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -25934,7 +25712,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SignedUnsignedExpr-ML_832</t>
+          <t xml:space="preserve">SignedUnsignedExpr-ML_799</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -25949,12 +25727,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -26076,7 +25854,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SignedUnsignedExpr-ML_833</t>
+          <t xml:space="preserve">SignedUnsignedExpr-ML_799</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -26091,12 +25869,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -26218,7 +25996,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SignedUnsignedExpr-ML_771</t>
+          <t xml:space="preserve">SignedUnsignedExpr-ML_799</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -26233,12 +26011,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -26316,6 +26094,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -26437,77 +26218,77 @@
           <t xml:space="preserve">waiver_timestamp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Violation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FileName</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineNumber</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Statement</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NodeName</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LHSExpr</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LHS_Size</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RHSExpr</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RHS_Size</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NodeType</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HIERARCHY</t>
         </is>
@@ -26536,7 +26317,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -26546,7 +26327,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -26576,7 +26357,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_808</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -26698,7 +26479,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -26708,7 +26489,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -26738,7 +26519,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_809</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -26860,7 +26641,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -26870,7 +26651,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -26900,7 +26681,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_814</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -27022,7 +26803,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -27032,7 +26813,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -27062,7 +26843,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_810</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -27184,7 +26965,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -27194,7 +26975,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -27224,7 +27005,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_813</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -27346,7 +27127,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -27356,7 +27137,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -27386,7 +27167,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_811</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -27508,7 +27289,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -27518,7 +27299,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -27548,7 +27329,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_811</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -27670,7 +27451,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -27680,7 +27461,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -27710,7 +27491,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_781</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -27832,7 +27613,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -27842,7 +27623,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -27872,7 +27653,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_815</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -27994,7 +27775,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -28004,7 +27785,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -28034,7 +27815,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_789</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -28156,7 +27937,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -28166,7 +27947,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -28196,7 +27977,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_790</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -28318,7 +28099,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -28328,7 +28109,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -28358,7 +28139,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_791</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -28480,7 +28261,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -28490,7 +28271,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -28520,7 +28301,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_792</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -28642,7 +28423,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -28652,7 +28433,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -28682,7 +28463,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_793</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -28804,7 +28585,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -28814,7 +28595,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -28844,7 +28625,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_793</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -28966,7 +28747,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -28976,7 +28757,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -29006,7 +28787,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_783</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -29128,7 +28909,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -29138,7 +28919,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -29168,7 +28949,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_784</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -29290,7 +29071,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -29300,7 +29081,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -29452,7 +29233,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -29462,7 +29243,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -29614,7 +29395,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -29624,7 +29405,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -29654,7 +29435,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_798</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -29776,7 +29557,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -29786,7 +29567,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -29816,7 +29597,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_802</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -29938,7 +29719,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -29948,7 +29729,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -29978,7 +29759,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_799</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -30100,7 +29881,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -30110,7 +29891,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -30140,7 +29921,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_800</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -30262,7 +30043,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -30272,7 +30053,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -30302,7 +30083,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_801</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -30424,7 +30205,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -30434,7 +30215,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -30464,7 +30245,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_803</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -30586,7 +30367,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -30596,7 +30377,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -30626,7 +30407,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_772</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -30748,7 +30529,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -30758,7 +30539,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -30788,7 +30569,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_773</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -30910,7 +30691,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -30920,7 +30701,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -30950,7 +30731,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_774</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -31072,7 +30853,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -31082,7 +30863,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -31112,7 +30893,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_775</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -31234,7 +31015,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -31244,7 +31025,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -31274,7 +31055,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_776</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -31396,7 +31177,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -31406,7 +31187,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -31436,7 +31217,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_777</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -31558,7 +31339,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -31568,7 +31349,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -31598,7 +31379,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_778</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -31720,7 +31501,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -31730,7 +31511,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -31760,7 +31541,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_779</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -31882,7 +31663,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -31892,7 +31673,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -31922,7 +31703,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_780</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -32044,7 +31825,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -32054,7 +31835,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -32084,7 +31865,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_806</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -32206,7 +31987,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -32216,7 +31997,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -32246,7 +32027,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_807</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -32368,7 +32149,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -32378,7 +32159,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -32408,7 +32189,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_816</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -32530,7 +32311,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -32540,7 +32321,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -32570,7 +32351,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_817</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -32692,7 +32473,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -32702,7 +32483,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -32732,7 +32513,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_818</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -32854,7 +32635,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -32864,7 +32645,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -32894,7 +32675,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_819</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -33016,7 +32797,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -33026,7 +32807,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -33056,7 +32837,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_820</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -33178,7 +32959,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -33188,7 +32969,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -33218,7 +32999,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_821</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -33340,7 +33121,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -33350,7 +33131,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -33380,7 +33161,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_822</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -33502,7 +33283,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -33512,7 +33293,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -33542,7 +33323,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_823</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -33664,7 +33445,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -33674,7 +33455,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -33704,7 +33485,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_824</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -33826,7 +33607,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -33836,7 +33617,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -33866,7 +33647,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_826</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -33988,7 +33769,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -33998,7 +33779,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -34028,7 +33809,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_827</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -34150,7 +33931,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -34160,7 +33941,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -34190,7 +33971,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_828</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -34312,7 +34093,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -34322,7 +34103,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -34352,7 +34133,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_829</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -34474,7 +34255,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -34484,7 +34265,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -34514,7 +34295,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_825</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -34636,7 +34417,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -34646,7 +34427,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -34676,7 +34457,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_839</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -34798,7 +34579,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -34808,7 +34589,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -34838,7 +34619,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_840</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -34960,7 +34741,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -34970,7 +34751,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -35000,7 +34781,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_841</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -35122,7 +34903,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -35132,7 +34913,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -35162,7 +34943,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_835</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -35284,7 +35065,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -35294,7 +35075,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -35324,7 +35105,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_836</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -35446,7 +35227,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">AUTO</t>
+          <t xml:space="preserve">CUSTOM</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -35456,7 +35237,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -35486,7 +35267,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">W164a_837</t>
+          <t xml:space="preserve">W164a_785</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -35604,6 +35385,9 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -35720,52 +35504,52 @@
           <t xml:space="preserve">waiver_timestamp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Violation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FileName</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineNumber</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Statement</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Signal</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HIERARCHY</t>
         </is>
@@ -35834,7 +35618,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_1000</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -35849,12 +35633,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -35971,7 +35755,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_911</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -35986,12 +35770,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -36108,7 +35892,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_912</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -36123,12 +35907,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -36245,7 +36029,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_907</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -36260,12 +36044,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -36382,7 +36166,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_905</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -36397,12 +36181,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -36519,7 +36303,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_908</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -36534,12 +36318,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -36656,7 +36440,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_906</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -36671,12 +36455,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -36793,7 +36577,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_910</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -36808,12 +36592,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -36930,7 +36714,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_909</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -36945,12 +36729,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -37067,7 +36851,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_903</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -37082,12 +36866,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -37204,7 +36988,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_940</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -37219,12 +37003,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -37341,7 +37125,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_915</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -37356,12 +37140,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -37478,7 +37262,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_914</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -37493,12 +37277,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -37615,7 +37399,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_902</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -37630,12 +37414,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -37752,7 +37536,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_863</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -37767,12 +37551,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -37889,7 +37673,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_943</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -37904,12 +37688,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -38026,7 +37810,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_858</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -38041,12 +37825,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -38163,7 +37947,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_859</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -38178,12 +37962,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -38300,7 +38084,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">W240_1011</t>
+          <t xml:space="preserve">W240_830</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -38315,12 +38099,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -38393,6 +38177,9 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -38508,47 +38295,47 @@
           <t xml:space="preserve">waiver_timestamp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Violation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FileName</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineNumber</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Statement</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">ModPortName</t>
         </is>
@@ -38617,7 +38404,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1001</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -38632,12 +38419,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -38749,7 +38536,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1002</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -38764,12 +38551,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -38881,7 +38668,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1001</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -38896,12 +38683,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -39013,7 +38800,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1002</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -39028,12 +38815,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -39145,7 +38932,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1001</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -39160,12 +38947,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -39277,7 +39064,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1002</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -39292,12 +39079,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -39409,7 +39196,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1001</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -39424,12 +39211,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -39541,7 +39328,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1002</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -39556,12 +39343,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -39673,7 +39460,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1001</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -39688,12 +39475,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -39805,7 +39592,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1002</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -39820,12 +39607,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -39937,7 +39724,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_938</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -39952,12 +39739,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -40069,7 +39856,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_939</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -40084,12 +39871,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -40201,7 +39988,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_941</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -40216,12 +40003,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -40333,7 +40120,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_942</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -40348,12 +40135,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -40465,7 +40252,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_917</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -40480,12 +40267,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -40597,7 +40384,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_918</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -40612,12 +40399,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -40729,7 +40516,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_919</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -40744,12 +40531,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -40861,7 +40648,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_922</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -40876,12 +40663,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -40993,7 +40780,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_923</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -41008,12 +40795,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -41125,7 +40912,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_864</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -41140,12 +40927,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -41257,7 +41044,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_865</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -41272,12 +41059,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -41389,7 +41176,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_866</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -41404,12 +41191,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -41521,7 +41308,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_867</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -41536,12 +41323,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -41653,7 +41440,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_868</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -41668,12 +41455,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -41785,7 +41572,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_869</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -41800,12 +41587,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -41917,7 +41704,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_870</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -41932,12 +41719,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -42049,7 +41836,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_925</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -42064,12 +41851,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -42181,7 +41968,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_926</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -42196,12 +41983,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -42313,7 +42100,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_927</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -42328,12 +42115,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -42445,7 +42232,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_928</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -42460,12 +42247,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -42577,7 +42364,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_929</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -42592,12 +42379,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -42709,7 +42496,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_930</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -42724,12 +42511,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -42841,7 +42628,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_931</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -42856,12 +42643,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -42973,7 +42760,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_932</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -42988,12 +42775,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -43105,7 +42892,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_933</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -43120,12 +42907,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -43237,7 +43024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_944</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -43252,12 +43039,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -43369,7 +43156,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_945</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -43384,12 +43171,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -43501,7 +43288,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_842</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -43516,12 +43303,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -43633,7 +43420,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_843</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -43648,12 +43435,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -43765,7 +43552,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_844</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -43780,12 +43567,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -43897,7 +43684,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_845</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -43912,12 +43699,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -44029,7 +43816,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_860</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -44044,12 +43831,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -44161,7 +43948,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_860</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -44176,12 +43963,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -44293,7 +44080,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1012</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -44308,12 +44095,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -44425,7 +44212,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1027</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -44440,12 +44227,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -44557,7 +44344,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1027</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -44572,12 +44359,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -44689,7 +44476,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1027</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -44704,12 +44491,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -44821,7 +44608,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1027</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -44836,12 +44623,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -44953,7 +44740,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1023</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -44968,12 +44755,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -45085,7 +44872,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1018</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -45100,12 +44887,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -45217,7 +45004,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1018</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -45232,12 +45019,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -45349,7 +45136,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1018</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -45364,12 +45151,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -45481,7 +45268,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1018</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -45496,12 +45283,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -45613,7 +45400,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">W287b_1014</t>
+          <t xml:space="preserve">W287b_800</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -45628,12 +45415,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -45701,6 +45488,9 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFFFA500"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -45821,72 +45611,72 @@
           <t xml:space="preserve">waiver_timestamp</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Tag</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Description</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Violation</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Goal</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Module</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FileName</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LineNumber</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Statement</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">OpType</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LHSExpr</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">LHS_Size</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RHSExpr</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RHS_Size</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HIERARCHY</t>
         </is>
@@ -45955,7 +45745,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t xml:space="preserve">W362_782</t>
+          <t xml:space="preserve">W362_786</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -45970,12 +45760,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -46112,7 +45902,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">W362_795</t>
+          <t xml:space="preserve">W362_786</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -46127,12 +45917,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -46269,7 +46059,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">W362_804</t>
+          <t xml:space="preserve">W362_786</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -46284,12 +46074,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R4" t="inlineStr">

--- a/LINT/outputs/lint_review.xlsx
+++ b/LINT/outputs/lint_review.xlsx
@@ -31,6 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'W551'!$A$1:$Z$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Instructions'!$A$1:$A$7</definedName>
   </definedNames>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -86,6 +87,71 @@
       <text>
         <t xml:space="preserve">full: the issue comes from report_lint.full
 waived: the issue comes from report_lint.waived</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <t xml:space="preserve">Generated waiver timestamp. Updated by gen_waiver when the IP owner changes the issue's owner fields or filter. Do not change manually.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
       </text>
     </comment>
   </commentList>
@@ -146,6 +212,66 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <t xml:space="preserve">Generated waiver timestamp. Updated by gen_waiver when the IP owner changes the issue's owner fields or filter. Do not change manually.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -202,6 +328,56 @@
       <text>
         <t xml:space="preserve">full: the issue comes from report_lint.full
 waived: the issue comes from report_lint.waived</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <t xml:space="preserve">Generated waiver timestamp. Updated by gen_waiver when the IP owner changes the issue's owner fields or filter. Do not change manually.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
       </text>
     </comment>
   </commentList>
@@ -262,6 +438,61 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <t xml:space="preserve">Generated waiver timestamp. Updated by gen_waiver when the IP owner changes the issue's owner fields or filter. Do not change manually.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -318,6 +549,71 @@
       <text>
         <t xml:space="preserve">full: the issue comes from report_lint.full
 waived: the issue comes from report_lint.waived</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <t xml:space="preserve">Generated waiver timestamp. Updated by gen_waiver when the IP owner changes the issue's owner fields or filter. Do not change manually.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
       </text>
     </comment>
   </commentList>
@@ -378,6 +674,66 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <t xml:space="preserve">Generated waiver timestamp. Updated by gen_waiver when the IP owner changes the issue's owner fields or filter. Do not change manually.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -434,6 +790,66 @@
       <text>
         <t xml:space="preserve">full: the issue comes from report_lint.full
 waived: the issue comes from report_lint.waived</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <t xml:space="preserve">Generated waiver timestamp. Updated by gen_waiver when the IP owner changes the issue's owner fields or filter. Do not change manually.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
       </text>
     </comment>
   </commentList>
@@ -494,6 +910,86 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <t xml:space="preserve">Generated waiver timestamp. Updated by gen_waiver when the IP owner changes the issue's owner fields or filter. Do not change manually.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AF1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -550,6 +1046,61 @@
       <text>
         <t xml:space="preserve">full: the issue comes from report_lint.full
 waived: the issue comes from report_lint.waived</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <t xml:space="preserve">Generated waiver timestamp. Updated by gen_waiver when the IP owner changes the issue's owner fields or filter. Do not change manually.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
       </text>
     </comment>
   </commentList>
@@ -610,6 +1161,56 @@
 waived: the issue comes from report_lint.waived</t>
       </text>
     </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <t xml:space="preserve">Generated waiver timestamp. Updated by gen_waiver when the IP owner changes the issue's owner fields or filter. Do not change manually.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -666,6 +1267,81 @@
       <text>
         <t xml:space="preserve">full: the issue comes from report_lint.full
 waived: the issue comes from report_lint.waived</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <t xml:space="preserve">Generated waiver timestamp. Updated by gen_waiver when the IP owner changes the issue's owner fields or filter. Do not change manually.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="0">
+      <text>
+        <t xml:space="preserve">Do not change</t>
       </text>
     </comment>
   </commentList>
@@ -744,13 +1420,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -796,35 +1472,30 @@
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t xml:space="preserve">DeadCode-ML</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32</t>
-        </is>
+      <c r="C2">
+        <f>COUNTA('DeadCode-ML'!$A$2:$A$33)</f>
+        <v>32</v>
+      </c>
+      <c r="D2">
+        <f>COUNTIF('DeadCode-ML'!$C$2:$C$33,"WAIVED")</f>
+        <v>32</v>
+      </c>
+      <c r="E2">
+        <f>COUNTIF('DeadCode-ML'!$C$2:$C$33,"UNREVIEWED")+COUNTBLANK('DeadCode-ML'!$C$2:$C$33)</f>
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <f>COUNTIF('DeadCode-ML'!$I$2:$I$33,"APPROVED")+COUNTIF('DeadCode-ML'!$I$2:$I$33,"DISAPPROVED")</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>COUNTIF('DeadCode-ML'!$I$2:$I$33,"PENDING")+COUNTBLANK('DeadCode-ML'!$I$2:$I$33)</f>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -833,35 +1504,30 @@
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t xml:space="preserve">MissingFsmStateTransition</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
+      <c r="C3">
+        <f>COUNTA('MissingFsmStateTransition'!$A$2:$A$4)</f>
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <f>COUNTIF('MissingFsmStateTransition'!$C$2:$C$4,"WAIVED")</f>
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <f>COUNTIF('MissingFsmStateTransition'!$C$2:$C$4,"UNREVIEWED")+COUNTBLANK('MissingFsmStateTransition'!$C$2:$C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>COUNTIF('MissingFsmStateTransition'!$I$2:$I$4,"APPROVED")+COUNTIF('MissingFsmStateTransition'!$I$2:$I$4,"DISAPPROVED")</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f>COUNTIF('MissingFsmStateTransition'!$I$2:$I$4,"PENDING")+COUNTBLANK('MissingFsmStateTransition'!$I$2:$I$4)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -870,35 +1536,30 @@
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t xml:space="preserve">NotReachableFsmState</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
+      <c r="C4">
+        <f>COUNTA('NotReachableFsmState'!$A$2:$A$5)</f>
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <f>COUNTIF('NotReachableFsmState'!$C$2:$C$5,"WAIVED")</f>
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <f>COUNTIF('NotReachableFsmState'!$C$2:$C$5,"UNREVIEWED")+COUNTBLANK('NotReachableFsmState'!$C$2:$C$5)</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>COUNTIF('NotReachableFsmState'!$I$2:$I$5,"APPROVED")+COUNTIF('NotReachableFsmState'!$I$2:$I$5,"DISAPPROVED")</f>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f>COUNTIF('NotReachableFsmState'!$I$2:$I$5,"PENDING")+COUNTBLANK('NotReachableFsmState'!$I$2:$I$5)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -907,35 +1568,30 @@
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t xml:space="preserve">SignedUnsignedExpr-ML</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
+      <c r="C5">
+        <f>COUNTA('SignedUnsignedExpr-ML'!$A$2:$A$8)</f>
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <f>COUNTIF('SignedUnsignedExpr-ML'!$C$2:$C$8,"WAIVED")</f>
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <f>COUNTIF('SignedUnsignedExpr-ML'!$C$2:$C$8,"UNREVIEWED")+COUNTBLANK('SignedUnsignedExpr-ML'!$C$2:$C$8)</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>COUNTIF('SignedUnsignedExpr-ML'!$I$2:$I$8,"APPROVED")+COUNTIF('SignedUnsignedExpr-ML'!$I$2:$I$8,"DISAPPROVED")</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f>COUNTIF('SignedUnsignedExpr-ML'!$I$2:$I$8,"PENDING")+COUNTBLANK('SignedUnsignedExpr-ML'!$I$2:$I$8)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -944,35 +1600,30 @@
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t xml:space="preserve">W164a</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56</t>
-        </is>
+      <c r="C6">
+        <f>COUNTA('W164a'!$A$2:$A$57)</f>
+        <v>56</v>
+      </c>
+      <c r="D6">
+        <f>COUNTIF('W164a'!$C$2:$C$57,"WAIVED")</f>
+        <v>56</v>
+      </c>
+      <c r="E6">
+        <f>COUNTIF('W164a'!$C$2:$C$57,"UNREVIEWED")+COUNTBLANK('W164a'!$C$2:$C$57)</f>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f>COUNTIF('W164a'!$I$2:$I$57,"APPROVED")+COUNTIF('W164a'!$I$2:$I$57,"DISAPPROVED")</f>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f>COUNTIF('W164a'!$I$2:$I$57,"PENDING")+COUNTBLANK('W164a'!$I$2:$I$57)</f>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -981,35 +1632,30 @@
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t xml:space="preserve">W240</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19</t>
-        </is>
+      <c r="C7">
+        <f>COUNTA('W240'!$A$2:$A$20)</f>
+        <v>19</v>
+      </c>
+      <c r="D7">
+        <f>COUNTIF('W240'!$C$2:$C$20,"WAIVED")</f>
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <f>COUNTIF('W240'!$C$2:$C$20,"UNREVIEWED")+COUNTBLANK('W240'!$C$2:$C$20)</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>COUNTIF('W240'!$I$2:$I$20,"APPROVED")+COUNTIF('W240'!$I$2:$I$20,"DISAPPROVED")</f>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f>COUNTIF('W240'!$I$2:$I$20,"PENDING")+COUNTBLANK('W240'!$I$2:$I$20)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1018,35 +1664,30 @@
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t xml:space="preserve">W287b</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54</t>
-        </is>
+      <c r="C8">
+        <f>COUNTA('W287b'!$A$2:$A$55)</f>
+        <v>54</v>
+      </c>
+      <c r="D8">
+        <f>COUNTIF('W287b'!$C$2:$C$55,"WAIVED")</f>
+        <v>54</v>
+      </c>
+      <c r="E8">
+        <f>COUNTIF('W287b'!$C$2:$C$55,"UNREVIEWED")+COUNTBLANK('W287b'!$C$2:$C$55)</f>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f>COUNTIF('W287b'!$I$2:$I$55,"APPROVED")+COUNTIF('W287b'!$I$2:$I$55,"DISAPPROVED")</f>
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <f>COUNTIF('W287b'!$I$2:$I$55,"PENDING")+COUNTBLANK('W287b'!$I$2:$I$55)</f>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1055,35 +1696,30 @@
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t xml:space="preserve">W362</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
+      <c r="C9">
+        <f>COUNTA('W362'!$A$2:$A$4)</f>
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <f>COUNTIF('W362'!$C$2:$C$4,"WAIVED")</f>
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <f>COUNTIF('W362'!$C$2:$C$4,"UNREVIEWED")+COUNTBLANK('W362'!$C$2:$C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <f>COUNTIF('W362'!$I$2:$I$4,"APPROVED")+COUNTIF('W362'!$I$2:$I$4,"DISAPPROVED")</f>
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <f>COUNTIF('W362'!$I$2:$I$4,"PENDING")+COUNTBLANK('W362'!$I$2:$I$4)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1092,35 +1728,30 @@
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t xml:space="preserve">W415a</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
+      <c r="C10">
+        <f>COUNTA('W415a'!$A$2:$A$4)</f>
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <f>COUNTIF('W415a'!$C$2:$C$4,"WAIVED")</f>
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <f>COUNTIF('W415a'!$C$2:$C$4,"UNREVIEWED")+COUNTBLANK('W415a'!$C$2:$C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f>COUNTIF('W415a'!$I$2:$I$4,"APPROVED")+COUNTIF('W415a'!$I$2:$I$4,"DISAPPROVED")</f>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f>COUNTIF('W415a'!$I$2:$I$4,"PENDING")+COUNTBLANK('W415a'!$I$2:$I$4)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1129,35 +1760,30 @@
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t xml:space="preserve">W528</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116</t>
-        </is>
+      <c r="C11">
+        <f>COUNTA('W528'!$A$2:$A$117)</f>
+        <v>116</v>
+      </c>
+      <c r="D11">
+        <f>COUNTIF('W528'!$C$2:$C$117,"WAIVED")</f>
+        <v>116</v>
+      </c>
+      <c r="E11">
+        <f>COUNTIF('W528'!$C$2:$C$117,"UNREVIEWED")+COUNTBLANK('W528'!$C$2:$C$117)</f>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <f>COUNTIF('W528'!$I$2:$I$117,"APPROVED")+COUNTIF('W528'!$I$2:$I$117,"DISAPPROVED")</f>
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <f>COUNTIF('W528'!$I$2:$I$117,"PENDING")+COUNTBLANK('W528'!$I$2:$I$117)</f>
+        <v>116</v>
       </c>
     </row>
     <row r="12">
@@ -1166,35 +1792,30 @@
           <t xml:space="preserve">warning</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">W551</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
+      <c r="C12">
+        <f>COUNTA('W551'!$A$2:$A$2)</f>
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <f>COUNTIF('W551'!$C$2:$C$2,"WAIVED")</f>
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <f>COUNTIF('W551'!$C$2:$C$2,"UNREVIEWED")+COUNTBLANK('W551'!$C$2:$C$2)</f>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f>COUNTIF('W551'!$I$2:$I$2,"APPROVED")+COUNTIF('W551'!$I$2:$I$2,"DISAPPROVED")</f>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f>COUNTIF('W551'!$I$2:$I$2,"PENDING")+COUNTBLANK('W551'!$I$2:$I$2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1208,30 +1829,25 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298</t>
-        </is>
+      <c r="C13">
+        <f>SUM(C2:C12)</f>
+        <v>298</v>
+      </c>
+      <c r="D13">
+        <f>SUM(D2:D12)</f>
+        <v>298</v>
+      </c>
+      <c r="E13">
+        <f>SUM(E2:E12)</f>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f>SUM(F2:F12)</f>
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <f>SUM(G2:G12)</f>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -1246,22 +1862,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1" hidden="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="72" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="13" max="13" width="72" customWidth="1" hidden="1"/>
+    <col min="14" max="14" width="18" customWidth="1" hidden="1"/>
+    <col min="15" max="15" width="18" customWidth="1" hidden="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" hidden="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -1334,7 +1950,7 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_status</t>
+          <t xml:space="preserve">Issue Status</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -1354,12 +1970,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_user</t>
+          <t xml:space="preserve">Time Stamp</t>
         </is>
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_timestamp</t>
+          <t xml:space="preserve">waiver_owner_signature</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -1890,22 +2506,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1" hidden="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="72" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="13" max="13" width="72" customWidth="1" hidden="1"/>
+    <col min="14" max="14" width="18" customWidth="1" hidden="1"/>
+    <col min="15" max="15" width="18" customWidth="1" hidden="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" hidden="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -1977,7 +2593,7 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_status</t>
+          <t xml:space="preserve">Issue Status</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -1997,12 +2613,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_user</t>
+          <t xml:space="preserve">Time Stamp</t>
         </is>
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_timestamp</t>
+          <t xml:space="preserve">waiver_owner_signature</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -18557,22 +19173,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1" hidden="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="72" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="13" max="13" width="72" customWidth="1" hidden="1"/>
+    <col min="14" max="14" width="18" customWidth="1" hidden="1"/>
+    <col min="15" max="15" width="18" customWidth="1" hidden="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" hidden="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -18642,7 +19258,7 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_status</t>
+          <t xml:space="preserve">Issue Status</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -18662,12 +19278,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_user</t>
+          <t xml:space="preserve">Time Stamp</t>
         </is>
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_timestamp</t>
+          <t xml:space="preserve">waiver_owner_signature</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -18739,7 +19355,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -18749,7 +19365,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -18794,12 +19410,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -18902,7 +19518,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waiver Tcl generation depends only on Owner Action = WAIVED.</t>
+          <t xml:space="preserve">Waiver Tcl generation requires Owner Action = WAIVED and uses IP Owner for -user.</t>
         </is>
       </c>
     </row>
@@ -18932,22 +19548,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1" hidden="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="72" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="13" max="13" width="72" customWidth="1" hidden="1"/>
+    <col min="14" max="14" width="18" customWidth="1" hidden="1"/>
+    <col min="15" max="15" width="18" customWidth="1" hidden="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" hidden="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -19018,7 +19634,7 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_status</t>
+          <t xml:space="preserve">Issue Status</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -19038,12 +19654,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_user</t>
+          <t xml:space="preserve">Time Stamp</t>
         </is>
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_timestamp</t>
+          <t xml:space="preserve">waiver_owner_signature</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -19120,7 +19736,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -19130,7 +19746,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -19175,12 +19791,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -19257,7 +19873,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -19267,7 +19883,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -19312,12 +19928,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -19394,7 +20010,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -19404,7 +20020,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -19449,12 +20065,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -19531,7 +20147,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -19541,7 +20157,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -19586,12 +20202,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -19668,7 +20284,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -19678,7 +20294,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -19723,12 +20339,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -19805,7 +20421,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -19815,7 +20431,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -19860,12 +20476,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -19942,7 +20558,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -19952,7 +20568,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -19997,12 +20613,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -20079,7 +20695,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -20089,7 +20705,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -20134,12 +20750,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -20216,7 +20832,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -20226,7 +20842,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -20271,12 +20887,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -20353,7 +20969,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -20363,7 +20979,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -20408,12 +21024,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -20490,7 +21106,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -20500,7 +21116,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -20545,12 +21161,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -20627,7 +21243,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -20637,7 +21253,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -20682,12 +21298,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -20764,7 +21380,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -20774,7 +21390,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -20819,12 +21435,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -20901,7 +21517,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -20911,7 +21527,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -20956,12 +21572,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -21038,7 +21654,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -21048,7 +21664,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -21093,12 +21709,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -21175,7 +21791,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -21185,7 +21801,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -21230,12 +21846,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -21312,7 +21928,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -21322,7 +21938,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -21367,12 +21983,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -21449,7 +22065,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -21459,7 +22075,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -21504,12 +22120,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -21586,7 +22202,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -21596,7 +22212,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -21641,12 +22257,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -21723,7 +22339,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -21733,7 +22349,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -21778,12 +22394,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -21860,7 +22476,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -21870,7 +22486,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -21915,12 +22531,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -21997,7 +22613,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -22007,7 +22623,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -22052,12 +22668,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -22134,7 +22750,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -22144,7 +22760,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -22189,12 +22805,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -22271,7 +22887,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -22281,7 +22897,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -22326,12 +22942,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -22408,7 +23024,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -22418,7 +23034,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -22463,12 +23079,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -22545,7 +23161,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -22555,7 +23171,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -22600,12 +23216,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -22682,7 +23298,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -22692,7 +23308,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -22737,12 +23353,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -22819,7 +23435,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -22829,7 +23445,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -22874,12 +23490,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -22956,7 +23572,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -22966,7 +23582,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -23011,12 +23627,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -23093,7 +23709,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -23103,7 +23719,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -23148,12 +23764,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -23230,7 +23846,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -23240,7 +23856,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -23285,12 +23901,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -23367,7 +23983,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -23377,7 +23993,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_DATAGEN")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -23422,12 +24038,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -23505,22 +24121,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1" hidden="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="72" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="13" max="13" width="72" customWidth="1" hidden="1"/>
+    <col min="14" max="14" width="18" customWidth="1" hidden="1"/>
+    <col min="15" max="15" width="18" customWidth="1" hidden="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" hidden="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -23593,7 +24209,7 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_status</t>
+          <t xml:space="preserve">Issue Status</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -23613,12 +24229,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_user</t>
+          <t xml:space="preserve">Time Stamp</t>
         </is>
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_timestamp</t>
+          <t xml:space="preserve">waiver_owner_signature</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -24147,22 +24763,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1" hidden="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="72" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="13" max="13" width="72" customWidth="1" hidden="1"/>
+    <col min="14" max="14" width="18" customWidth="1" hidden="1"/>
+    <col min="15" max="15" width="18" customWidth="1" hidden="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" hidden="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -24234,7 +24850,7 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_status</t>
+          <t xml:space="preserve">Issue Status</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -24254,12 +24870,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_user</t>
+          <t xml:space="preserve">Time Stamp</t>
         </is>
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_timestamp</t>
+          <t xml:space="preserve">waiver_owner_signature</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -24910,22 +25526,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1" hidden="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="72" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="13" max="13" width="72" customWidth="1" hidden="1"/>
+    <col min="14" max="14" width="18" customWidth="1" hidden="1"/>
+    <col min="15" max="15" width="18" customWidth="1" hidden="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" hidden="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -24997,7 +25613,7 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_status</t>
+          <t xml:space="preserve">Issue Status</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -25017,12 +25633,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_user</t>
+          <t xml:space="preserve">Time Stamp</t>
         </is>
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_timestamp</t>
+          <t xml:space="preserve">waiver_owner_signature</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -26099,22 +26715,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1" hidden="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="72" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="13" max="13" width="72" customWidth="1" hidden="1"/>
+    <col min="14" max="14" width="18" customWidth="1" hidden="1"/>
+    <col min="15" max="15" width="18" customWidth="1" hidden="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" hidden="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -26190,7 +26806,7 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_status</t>
+          <t xml:space="preserve">Issue Status</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -26210,12 +26826,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_user</t>
+          <t xml:space="preserve">Time Stamp</t>
         </is>
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_timestamp</t>
+          <t xml:space="preserve">waiver_owner_signature</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -26317,7 +26933,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -26327,7 +26943,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -26372,12 +26988,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -26479,7 +27095,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -26489,7 +27105,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -26534,12 +27150,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -26641,7 +27257,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -26651,7 +27267,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -26696,12 +27312,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -26803,7 +27419,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -26813,7 +27429,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -26858,12 +27474,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -26965,7 +27581,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -26975,7 +27591,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -27020,12 +27636,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -27127,7 +27743,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -27137,7 +27753,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -27182,12 +27798,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -27289,7 +27905,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -27299,7 +27915,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -27344,12 +27960,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -27451,7 +28067,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -27461,7 +28077,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -27506,12 +28122,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -27613,7 +28229,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -27623,7 +28239,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -27668,12 +28284,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -27775,7 +28391,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -27785,7 +28401,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -27830,12 +28446,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -27937,7 +28553,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -27947,7 +28563,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -27992,12 +28608,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -28099,7 +28715,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -28109,7 +28725,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -28154,12 +28770,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -28261,7 +28877,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -28271,7 +28887,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -28316,12 +28932,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -28423,7 +29039,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -28433,7 +29049,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -28478,12 +29094,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -28585,7 +29201,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -28595,7 +29211,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -28640,12 +29256,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -28747,7 +29363,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -28757,7 +29373,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -28802,12 +29418,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -28909,7 +29525,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -28919,7 +29535,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -28964,12 +29580,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -29071,7 +29687,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -29081,7 +29697,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -29126,12 +29742,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -29233,7 +29849,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -29243,7 +29859,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -29288,12 +29904,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -29395,7 +30011,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -29405,7 +30021,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -29450,12 +30066,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -29557,7 +30173,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -29567,7 +30183,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -29612,12 +30228,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -29719,7 +30335,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -29729,7 +30345,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -29774,12 +30390,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -29881,7 +30497,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -29891,7 +30507,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -29936,12 +30552,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -30043,7 +30659,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -30053,7 +30669,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -30098,12 +30714,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -30205,7 +30821,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -30215,7 +30831,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -30260,12 +30876,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -30367,7 +30983,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -30377,7 +30993,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -30422,12 +31038,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -30529,7 +31145,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -30539,7 +31155,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -30584,12 +31200,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -30691,7 +31307,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -30701,7 +31317,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -30746,12 +31362,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -30853,7 +31469,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -30863,7 +31479,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -30908,12 +31524,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -31015,7 +31631,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -31025,7 +31641,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -31070,12 +31686,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -31177,7 +31793,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -31187,7 +31803,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -31232,12 +31848,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -31339,7 +31955,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -31349,7 +31965,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -31394,12 +32010,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -31501,7 +32117,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -31511,7 +32127,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -31556,12 +32172,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -31663,7 +32279,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -31673,7 +32289,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -31718,12 +32334,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -31825,7 +32441,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -31835,7 +32451,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -31880,12 +32496,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -31987,7 +32603,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -31997,7 +32613,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -32042,12 +32658,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -32149,7 +32765,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -32159,7 +32775,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -32204,12 +32820,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -32311,7 +32927,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -32321,7 +32937,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -32366,12 +32982,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -32473,7 +33089,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -32483,7 +33099,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -32528,12 +33144,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -32635,7 +33251,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -32645,7 +33261,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -32690,12 +33306,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -32797,7 +33413,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -32807,7 +33423,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -32852,12 +33468,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -32959,7 +33575,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -32969,7 +33585,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -33014,12 +33630,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -33121,7 +33737,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -33131,7 +33747,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -33176,12 +33792,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -33283,7 +33899,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -33293,7 +33909,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -33338,12 +33954,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -33445,7 +34061,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -33455,7 +34071,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -33500,12 +34116,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -33607,7 +34223,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -33617,7 +34233,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -33662,12 +34278,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -33769,7 +34385,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -33779,7 +34395,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -33824,12 +34440,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -33931,7 +34547,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -33941,7 +34557,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -33986,12 +34602,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -34093,7 +34709,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -34103,7 +34719,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -34148,12 +34764,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -34255,7 +34871,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -34265,7 +34881,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -34310,12 +34926,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -34417,7 +35033,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -34427,7 +35043,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -34472,12 +35088,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -34579,7 +35195,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -34589,7 +35205,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -34634,12 +35250,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -34741,7 +35357,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -34751,7 +35367,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -34796,12 +35412,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -34903,7 +35519,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -34913,7 +35529,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -34958,12 +35574,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -35065,7 +35681,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -35075,7 +35691,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -35120,12 +35736,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -35227,7 +35843,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">CUSTOM</t>
+          <t xml:space="preserve">AUTO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -35237,7 +35853,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Goal == "BOS_LINT_RULE") AND (Module == "AESDMA_RD_DESC") AND (Statement =~ "*n_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] = r_rdAddr[AXI_ADDR_WD-1:ADDR_BASE_LSB] + {{(AXI_ADDR_WD-ADDR_BASE_LSB-AXI_LEN_WD){1'b0}}, w_rdBurstLen} + 1;*") AND (HIERARCHY == ":BOS_AESDMA:u_AESDMA_TOP@AESDMA_TOP_DCLS:u_aesdma_top@AESDMA_TOP:u_AESDMA_RD_DESC@AESDMA_RD_DESC")</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -35282,12 +35898,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t xml:space="preserve">pnson</t>
+          <t xml:space="preserve">21-09-2026 19:09:14</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-09-2026 19:09:14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -35390,22 +36006,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1" hidden="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="72" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="13" max="13" width="72" customWidth="1" hidden="1"/>
+    <col min="14" max="14" width="18" customWidth="1" hidden="1"/>
+    <col min="15" max="15" width="18" customWidth="1" hidden="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" hidden="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -35476,7 +36092,7 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_status</t>
+          <t xml:space="preserve">Issue Status</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -35496,12 +36112,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_user</t>
+          <t xml:space="preserve">Time Stamp</t>
         </is>
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_timestamp</t>
+          <t xml:space="preserve">waiver_owner_signature</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -38182,22 +38798,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1" hidden="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="72" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="13" max="13" width="72" customWidth="1" hidden="1"/>
+    <col min="14" max="14" width="18" customWidth="1" hidden="1"/>
+    <col min="15" max="15" width="18" customWidth="1" hidden="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" hidden="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -38267,7 +38883,7 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_status</t>
+          <t xml:space="preserve">Issue Status</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -38287,12 +38903,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_user</t>
+          <t xml:space="preserve">Time Stamp</t>
         </is>
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_timestamp</t>
+          <t xml:space="preserve">waiver_owner_signature</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
@@ -45493,22 +46109,22 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="64" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="30" customWidth="1"/>
+    <col min="11" max="11" width="64" customWidth="1" hidden="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="72" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="13" max="13" width="72" customWidth="1" hidden="1"/>
+    <col min="14" max="14" width="18" customWidth="1" hidden="1"/>
+    <col min="15" max="15" width="18" customWidth="1" hidden="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1" hidden="1"/>
     <col min="18" max="18" width="18" customWidth="1"/>
     <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
@@ -45583,7 +46199,7 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">record_status</t>
+          <t xml:space="preserve">Issue Status</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
@@ -45603,12 +46219,12 @@
       </c>
       <c r="P1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_user</t>
+          <t xml:space="preserve">Time Stamp</t>
         </is>
       </c>
       <c r="Q1" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waiver_timestamp</t>
+          <t xml:space="preserve">waiver_owner_signature</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
